--- a/results.xlsx
+++ b/results.xlsx
@@ -1,93 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_085D6A57D555AC5FE455CCB743245E3FB48F8F0A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A8C99B7-82B6-4A03-8520-7CD42AD66B81}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Best Parameters</t>
-  </si>
-  <si>
-    <t>CV Balanced Accuracy</t>
-  </si>
-  <si>
-    <t>Test Balanced Accuracy</t>
-  </si>
-  <si>
-    <t>XGBoost</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 5, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
-  </si>
-  <si>
-    <t>SVM</t>
-  </si>
-  <si>
-    <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
-  </si>
-  <si>
-    <t>Bin size</t>
-  </si>
-  <si>
-    <t>8ms</t>
-  </si>
-  <si>
-    <t>Z-thresh</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,57 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -434,89 +420,339 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>0.84325396825396826</v>
-      </c>
-      <c r="D2">
-        <v>0.90909090909090917</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>0.68055555555555547</v>
-      </c>
-      <c r="D3">
-        <v>0.62121212121212122</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>0.61507936507936511</v>
-      </c>
-      <c r="D4">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Best Parameters</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CV Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Test Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bin size</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Z-thresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 5, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8432539682539683</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8ms</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6805555555555555</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6212121212121212</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8ms</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6150793650793651</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8ms</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16ms</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8464285714285714</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16ms</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16ms</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6805555555555555</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4ms</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 7, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8551587301587302</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4ms</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4ms</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6805555555555555</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 7, 'xgb__min_child_weight': 5, 'xgb__n_estimators': 300, 'xgb__subsample': 1.0}</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.8535714285714286</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_085D371F925A220F62355476585DE6FC877B9C12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2775983C-6DD9-41E9-96D7-D29937E0BF1C}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_085D9FAF5645420E6235547658B456798D7B9D10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A3A2697-FE43-4D3E-8262-A736F1C7245B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
   <si>
     <t>Model</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 5, 'xgb__min_child_weight': 5, 'xgb__n_estimators': 300, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>Min_duration</t>
   </si>
 </sst>
 </file>
@@ -105,7 +114,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -128,13 +137,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -439,10 +462,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,8 +484,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -481,8 +507,11 @@
       <c r="F2">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -501,8 +530,11 @@
       <c r="F3">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -521,8 +553,11 @@
       <c r="F4">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -541,8 +576,11 @@
       <c r="F5">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -561,8 +599,11 @@
       <c r="F6">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -581,8 +622,11 @@
       <c r="F7">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -601,8 +645,11 @@
       <c r="F8">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -621,8 +668,11 @@
       <c r="F9">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -640,6 +690,78 @@
       </c>
       <c r="F10">
         <v>2.5</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>0.76309523809523805</v>
+      </c>
+      <c r="D11">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11">
+        <v>2.5</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>0.61309523809523814</v>
+      </c>
+      <c r="D12">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12">
+        <v>2.5</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>0.6694444444444444</v>
+      </c>
+      <c r="D13">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13">
+        <v>2.5</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_085D9FAF5645420E6235547658B456798D7B9D10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A3A2697-FE43-4D3E-8262-A736F1C7245B}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_085DCDDF97718C0F62355476581046FC943191CB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACF55DA3-4876-46E1-BDDD-00A20787E9CD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="25">
   <si>
     <t>Model</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Z-thresh</t>
   </si>
   <si>
+    <t>Min_duration</t>
+  </si>
+  <si>
     <t>XGBoost</t>
   </si>
   <si>
@@ -85,7 +88,13 @@
     <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
   </si>
   <si>
-    <t>Min_duration</t>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 5, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
   </si>
 </sst>
 </file>
@@ -114,7 +123,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -137,27 +146,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -462,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -484,16 +479,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>21</v>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>0.84325396825396826</v>
@@ -502,7 +497,7 @@
         <v>0.90909090909090917</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>2.5</v>
@@ -513,10 +508,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>0.68055555555555547</v>
@@ -525,7 +520,7 @@
         <v>0.62121212121212122</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>2.5</v>
@@ -536,10 +531,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>0.61507936507936511</v>
@@ -548,7 +543,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>2.5</v>
@@ -559,10 +554,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>0.72222222222222221</v>
@@ -571,7 +566,7 @@
         <v>0.5757575757575758</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>2.5</v>
@@ -582,10 +577,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>0.84642857142857142</v>
@@ -594,7 +589,7 @@
         <v>0.45454545454545447</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>2.5</v>
@@ -605,10 +600,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>0.66666666666666663</v>
@@ -617,7 +612,7 @@
         <v>0.45454545454545447</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>2.5</v>
@@ -628,10 +623,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>0.68055555555555547</v>
@@ -640,7 +635,7 @@
         <v>0.5757575757575758</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>2.5</v>
@@ -651,10 +646,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>0.85515873015873023</v>
@@ -663,7 +658,7 @@
         <v>0.78787878787878785</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9">
         <v>2.5</v>
@@ -674,10 +669,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>0.54166666666666663</v>
@@ -686,7 +681,7 @@
         <v>0.53030303030303028</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10">
         <v>2.5</v>
@@ -697,10 +692,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>0.76309523809523805</v>
@@ -709,7 +704,7 @@
         <v>0.5757575757575758</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>2.5</v>
@@ -720,10 +715,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>0.61309523809523814</v>
@@ -732,7 +727,7 @@
         <v>0.40909090909090912</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12">
         <v>2.5</v>
@@ -743,10 +738,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>0.6694444444444444</v>
@@ -755,12 +750,127 @@
         <v>0.62121212121212122</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13">
         <v>2.5</v>
       </c>
       <c r="G13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>0.7686507936507937</v>
+      </c>
+      <c r="D14">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14">
+        <v>2.5</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15">
+        <v>0.57142857142857151</v>
+      </c>
+      <c r="D15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <v>2.5</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16">
+        <v>0.58531746031746035</v>
+      </c>
+      <c r="D16">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>2.5</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>0.62420634920634921</v>
+      </c>
+      <c r="D17">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <v>2.5</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>0.62420634920634921</v>
+      </c>
+      <c r="D18">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>2.5</v>
+      </c>
+      <c r="G18">
         <v>10</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_085DCDDF97718C0F62355476581046FC943191CB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACF55DA3-4876-46E1-BDDD-00A20787E9CD}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_085D1BEF9650AEFEEB731CF451245E3FB48F8978" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E8161B8-B853-48D6-8528-E40D083E68FE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Model</t>
   </si>
@@ -46,10 +46,13 @@
     <t>XGBoost</t>
   </si>
   <si>
-    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 5, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
-  </si>
-  <si>
-    <t>8ms</t>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
   </si>
   <si>
     <t>SVM</t>
@@ -58,50 +61,17 @@
     <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
   </si>
   <si>
-    <t>RF</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
-  </si>
-  <si>
-    <t>16ms</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+    <t>2.5</t>
   </si>
   <si>
     <t>4ms</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 7, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 5, 'xgb__min_child_weight': 5, 'xgb__n_estimators': 300, 'xgb__subsample': 1.0}</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 5, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 1.0}</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,6 +83,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -457,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -491,16 +467,16 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>0.84325396825396826</v>
+        <v>0.74642857142857144</v>
       </c>
       <c r="D2">
-        <v>0.90909090909090917</v>
+        <v>0.74242424242424243</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>2.5</v>
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -508,22 +484,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
       <c r="C3">
-        <v>0.68055555555555547</v>
+        <v>0.75476190476190474</v>
       </c>
       <c r="D3">
-        <v>0.62121212121212122</v>
+        <v>0.90909090909090917</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>2.5</v>
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -531,350 +507,29 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4">
+        <v>0.79841269841269835</v>
+      </c>
+      <c r="D4">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4">
-        <v>0.61507936507936511</v>
-      </c>
-      <c r="D4">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>2.5</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>0.72222222222222221</v>
-      </c>
-      <c r="D5">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>2.5</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>0.84642857142857142</v>
-      </c>
-      <c r="D6">
-        <v>0.45454545454545447</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>2.5</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D7">
-        <v>0.45454545454545447</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>2.5</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>0.68055555555555547</v>
-      </c>
-      <c r="D8">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8">
-        <v>2.5</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9">
-        <v>0.85515873015873023</v>
-      </c>
-      <c r="D9">
-        <v>0.78787878787878785</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>2.5</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D10">
-        <v>0.53030303030303028</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10">
-        <v>2.5</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>0.76309523809523805</v>
-      </c>
-      <c r="D11">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11">
-        <v>2.5</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12">
-        <v>0.61309523809523814</v>
-      </c>
-      <c r="D12">
-        <v>0.40909090909090912</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12">
-        <v>2.5</v>
-      </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>0.6694444444444444</v>
-      </c>
-      <c r="D13">
-        <v>0.62121212121212122</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13">
-        <v>2.5</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14">
-        <v>0.7686507936507937</v>
-      </c>
-      <c r="D14">
-        <v>0.78787878787878785</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14">
-        <v>2.5</v>
-      </c>
-      <c r="G14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15">
-        <v>0.57142857142857151</v>
-      </c>
-      <c r="D15">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15">
-        <v>2.5</v>
-      </c>
-      <c r="G15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16">
-        <v>0.58531746031746035</v>
-      </c>
-      <c r="D16">
-        <v>0.45454545454545447</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16">
-        <v>2.5</v>
-      </c>
-      <c r="G16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17">
-        <v>0.62420634920634921</v>
-      </c>
-      <c r="D17">
-        <v>0.45454545454545447</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17">
-        <v>2.5</v>
-      </c>
-      <c r="G17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18">
-        <v>0.62420634920634921</v>
-      </c>
-      <c r="D18">
-        <v>0.45454545454545447</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18">
-        <v>2.5</v>
-      </c>
-      <c r="G18">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results.xlsx
+++ b/results.xlsx
@@ -1,99 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_085D1BEF9650AEFEEB731CF451245E3FB48F8978" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E8161B8-B853-48D6-8528-E40D083E68FE}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Best Parameters</t>
-  </si>
-  <si>
-    <t>CV Balanced Accuracy</t>
-  </si>
-  <si>
-    <t>Test Balanced Accuracy</t>
-  </si>
-  <si>
-    <t>Bin size</t>
-  </si>
-  <si>
-    <t>Z-thresh</t>
-  </si>
-  <si>
-    <t>Min_duration</t>
-  </si>
-  <si>
-    <t>XGBoost</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
-  </si>
-  <si>
-    <t>RF</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
-  </si>
-  <si>
-    <t>SVM</t>
-  </si>
-  <si>
-    <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>4ms</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -108,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -432,104 +420,622 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Best Parameters</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CV Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Test Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bin size</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Z-thresh</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Min_duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7464285714285714</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4ms</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>0.74642857142857144</v>
-      </c>
-      <c r="D2">
-        <v>0.74242424242424243</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7547619047619047</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4ms</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>0.75476190476190474</v>
-      </c>
-      <c r="D3">
-        <v>0.90909090909090917</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7984126984126984</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4ms</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>0.79841269841269835</v>
-      </c>
-      <c r="D4">
-        <v>0.90909090909090917</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7567460317460317</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_085D730F1549B00F62355476583D56FF8AF39E75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C062C203-703F-4830-8579-D557A773F9E3}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_085DA73715662C0F623554765895DE78A4F1947B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5845A465-7724-4133-B8DC-F5279EA2D32F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
   <si>
     <t>Model</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
   </si>
 </sst>
 </file>
@@ -100,12 +106,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -135,11 +147,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -469,71 +482,71 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>0.74642857142857144</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>0.74242424242424243</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>2.5</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>0.75476190476190474</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>0.90909090909090917</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3">
-        <v>2.5</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G3" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>0.79841269841269835</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>0.90909090909090917</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4">
-        <v>2.5</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -653,25 +666,25 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>0.82896825396825402</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>0.86363636363636365</v>
       </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10">
-        <v>2.5</v>
-      </c>
-      <c r="G10">
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G10" s="2">
         <v>3</v>
       </c>
     </row>
@@ -722,26 +735,95 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>0.81269841269841281</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>0.78787878787878785</v>
       </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13">
-        <v>2.5</v>
-      </c>
-      <c r="G13">
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G13" s="2">
         <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>0.57817460317460323</v>
+      </c>
+      <c r="D14">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>2.5</v>
+      </c>
+      <c r="G14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>0.59484126984126984</v>
+      </c>
+      <c r="D15">
+        <v>0.4242424242424242</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>2.5</v>
+      </c>
+      <c r="G15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>0.59126984126984128</v>
+      </c>
+      <c r="D16">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16">
+        <v>2.5</v>
+      </c>
+      <c r="G16">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_085DA73715662C0F623554765895DE78A4F1947B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5845A465-7724-4133-B8DC-F5279EA2D32F}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_085D1D47D46BDA0F6235547658405EFB9DA5904B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8DB5F3-6C6B-4232-A799-A5C33D78C897}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="24">
   <si>
     <t>Model</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
   </si>
 </sst>
 </file>
@@ -106,18 +112,12 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -147,12 +147,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -482,71 +481,71 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>0.74642857142857144</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>0.74242424242424243</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F2">
+        <v>2.5</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>0.75476190476190474</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>0.90909090909090917</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="F3">
+        <v>2.5</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
         <v>0.79841269841269835</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>0.90909090909090917</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="F4">
+        <v>2.5</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -666,25 +665,25 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10">
         <v>0.82896825396825402</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10">
         <v>0.86363636363636365</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10">
+        <v>2.5</v>
+      </c>
+      <c r="G10">
         <v>3</v>
       </c>
     </row>
@@ -735,25 +734,25 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
         <v>0.81269841269841281</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>0.78787878787878785</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G13" s="2">
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>2.5</v>
+      </c>
+      <c r="G13">
         <v>30</v>
       </c>
     </row>
@@ -823,6 +822,75 @@
         <v>2.5</v>
       </c>
       <c r="G16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>0.66706349206349203</v>
+      </c>
+      <c r="D17">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>0.55158730158730152</v>
+      </c>
+      <c r="D18">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>0.60317460317460325</v>
+      </c>
+      <c r="D19">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
         <v>150</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_085D1D47D46BDA0F6235547658405EFB9DA5904B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8DB5F3-6C6B-4232-A799-A5C33D78C897}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_1EE9D7F4136D540F62355476585DCE3A87468CB8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC52B072-223B-44A9-AAE2-D0032DDA15BC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="78">
   <si>
     <t>Model</t>
   </si>
@@ -43,6 +43,12 @@
     <t>Min_duration</t>
   </si>
   <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
     <t>XGBoost</t>
   </si>
   <si>
@@ -64,34 +70,190 @@
     <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'linear'}</t>
   </si>
   <si>
-    <t>0,2ms</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 500}</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+    <t>0.2ms</t>
+  </si>
+  <si>
+    <t>MEAN:</t>
+  </si>
+  <si>
+    <t>STD:</t>
+  </si>
+  <si>
+    <t>0.7452</t>
+  </si>
+  <si>
+    <t>0.1346</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
   </si>
   <si>
     <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
   </si>
   <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 5, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 10, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>0.6882</t>
+  </si>
+  <si>
+    <t>0.1530</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
     <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
   </si>
   <si>
-    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
-  </si>
-  <si>
-    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
-  </si>
-  <si>
-    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>0.6988</t>
+  </si>
+  <si>
+    <t>0.1700</t>
   </si>
 </sst>
 </file>
@@ -454,10 +616,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,13 +641,19 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>0.74642857142857144</v>
@@ -494,7 +662,7 @@
         <v>0.74242424242424243</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>2.5</v>
@@ -503,12 +671,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0.75476190476190474</v>
@@ -517,7 +685,7 @@
         <v>0.90909090909090917</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2.5</v>
@@ -526,12 +694,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>0.79841269841269835</v>
@@ -540,7 +708,7 @@
         <v>0.90909090909090917</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>2.5</v>
@@ -549,159 +717,159 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>0.84007936507936509</v>
+        <v>0.74007936507936511</v>
       </c>
       <c r="D5">
-        <v>0.69696969696969702</v>
+        <v>0.81818181818181812</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5">
         <v>2.5</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6">
-        <v>0.76587301587301582</v>
+        <v>0.69523809523809532</v>
       </c>
       <c r="D6">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>2.5</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>0.70714285714285718</v>
+      </c>
+      <c r="D7">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>2.5</v>
+      </c>
+      <c r="G7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>0.54523809523809519</v>
+      </c>
+      <c r="D8">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8">
+        <v>2.5</v>
+      </c>
+      <c r="G8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="D9">
         <v>0.53030303030303028</v>
       </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>2.5</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>0.79126984126984123</v>
-      </c>
-      <c r="D7">
-        <v>0.65151515151515149</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>2.5</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>0.84007936507936509</v>
-      </c>
-      <c r="D8">
-        <v>0.69696969696969702</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8">
-        <v>2.5</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>0.79841269841269835</v>
-      </c>
-      <c r="D9">
-        <v>0.5757575757575758</v>
-      </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9">
         <v>2.5</v>
       </c>
       <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>0.82896825396825402</v>
+        <v>0.57420634920634928</v>
       </c>
       <c r="D10">
-        <v>0.86363636363636365</v>
+        <v>0.90909090909090917</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <v>2.5</v>
       </c>
       <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>0.80436507936507928</v>
+        <v>0.53650793650793649</v>
       </c>
       <c r="D11">
         <v>0.65151515151515149</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11">
         <v>2.5</v>
@@ -710,21 +878,21 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>0.76388888888888884</v>
+        <v>0.75595238095238104</v>
       </c>
       <c r="D12">
-        <v>0.69696969696969702</v>
+        <v>0.60606060606060597</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12">
         <v>2.5</v>
@@ -733,21 +901,21 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>0.81269841269841281</v>
+        <v>0.61071428571428577</v>
       </c>
       <c r="D13">
-        <v>0.78787878787878785</v>
+        <v>0.74242424242424243</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F13">
         <v>2.5</v>
@@ -756,142 +924,3271 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>0.57817460317460323</v>
+        <v>0.73095238095238102</v>
       </c>
       <c r="D14">
-        <v>0.81818181818181812</v>
+        <v>0.68181818181818188</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F14">
         <v>2.5</v>
       </c>
       <c r="G14">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C15">
-        <v>0.59484126984126984</v>
+        <v>0.50436507936507935</v>
       </c>
       <c r="D15">
-        <v>0.4242424242424242</v>
+        <v>0.90909090909090917</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15">
         <v>2.5</v>
       </c>
       <c r="G15">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>0.59126984126984128</v>
+        <v>0.79682539682539699</v>
       </c>
       <c r="D16">
-        <v>0.5757575757575758</v>
+        <v>0.56060606060606055</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F16">
         <v>2.5</v>
       </c>
       <c r="G16">
-        <v>150</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>0.66706349206349203</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="D17">
-        <v>0.69696969696969702</v>
+        <v>0.68181818181818188</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G17">
-        <v>150</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>0.55158730158730152</v>
+        <v>0.62817460317460316</v>
       </c>
       <c r="D18">
-        <v>0.74242424242424243</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G18">
-        <v>150</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>0.76825396825396819</v>
+      </c>
+      <c r="D19">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19">
+        <v>2.5</v>
+      </c>
+      <c r="G19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <v>0.54960317460317454</v>
+      </c>
+      <c r="D20">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20">
+        <v>2.5</v>
+      </c>
+      <c r="G20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21">
+        <v>0.75952380952380949</v>
+      </c>
+      <c r="D21">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21">
+        <v>2.5</v>
+      </c>
+      <c r="G21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22">
+        <v>0.62857142857142856</v>
+      </c>
+      <c r="D22">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22">
+        <v>2.5</v>
+      </c>
+      <c r="G22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>0.7146825396825397</v>
+      </c>
+      <c r="D23">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23">
+        <v>2.5</v>
+      </c>
+      <c r="G23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24">
+        <v>0.74722222222222223</v>
+      </c>
+      <c r="D24">
+        <v>0.51515151515151514</v>
+      </c>
+      <c r="E24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24">
+        <v>2.5</v>
+      </c>
+      <c r="G24">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25">
+        <v>0.69603174603174589</v>
+      </c>
+      <c r="D25">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25">
+        <v>2.5</v>
+      </c>
+      <c r="G25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26">
+        <v>0.58650793650793653</v>
+      </c>
+      <c r="D26">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26">
+        <v>2.5</v>
+      </c>
+      <c r="G26">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>0.71746031746031758</v>
+      </c>
+      <c r="D27">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27">
+        <v>2.5</v>
+      </c>
+      <c r="G27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28">
+        <v>0.71428571428571441</v>
+      </c>
+      <c r="D28">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28">
+        <v>2.5</v>
+      </c>
+      <c r="G28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29">
+        <v>0.76904761904761898</v>
+      </c>
+      <c r="D29">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29">
+        <v>2.5</v>
+      </c>
+      <c r="G29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30">
+        <v>0.74206349206349209</v>
+      </c>
+      <c r="D30">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30">
+        <v>2.5</v>
+      </c>
+      <c r="G30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31">
+        <v>0.61944444444444446</v>
+      </c>
+      <c r="D31">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31">
+        <v>2.5</v>
+      </c>
+      <c r="G31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <v>0.71547619047619049</v>
+      </c>
+      <c r="D32">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32">
+        <v>2.5</v>
+      </c>
+      <c r="G32">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33">
+        <v>2.5</v>
+      </c>
+      <c r="G33">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>0.85873015873015868</v>
+      </c>
+      <c r="D34">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E34" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34">
+        <v>2.5</v>
+      </c>
+      <c r="G34">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35">
+        <v>0.76507936507936503</v>
+      </c>
+      <c r="D35">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E35" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35">
+        <v>2.5</v>
+      </c>
+      <c r="G35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36">
+        <v>0.63769841269841265</v>
+      </c>
+      <c r="D36">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E36" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36">
+        <v>2.5</v>
+      </c>
+      <c r="G36">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>0.51428571428571435</v>
+      </c>
+      <c r="D37">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37">
+        <v>2.5</v>
+      </c>
+      <c r="G37">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>0.83452380952380956</v>
+      </c>
+      <c r="D38">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38">
+        <v>2.5</v>
+      </c>
+      <c r="G38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>0.71746031746031746</v>
+      </c>
+      <c r="D39">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E39" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39">
+        <v>2.5</v>
+      </c>
+      <c r="G39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40">
+        <v>0.67380952380952375</v>
+      </c>
+      <c r="D40">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E40" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40">
+        <v>2.5</v>
+      </c>
+      <c r="G40">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <v>0.70873015873015888</v>
+      </c>
+      <c r="D41">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E41" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41">
+        <v>2.5</v>
+      </c>
+      <c r="G41">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <v>0.59404761904761905</v>
+      </c>
+      <c r="D42">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E42" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42">
+        <v>2.5</v>
+      </c>
+      <c r="G42">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43">
+        <v>0.74047619047619051</v>
+      </c>
+      <c r="D43">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E43" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43">
+        <v>2.5</v>
+      </c>
+      <c r="G43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44">
+        <v>0.6246031746031746</v>
+      </c>
+      <c r="D44">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E44" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44">
+        <v>2.5</v>
+      </c>
+      <c r="G44">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45">
+        <v>0.68293650793650806</v>
+      </c>
+      <c r="D45">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45">
+        <v>2.5</v>
+      </c>
+      <c r="G45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46">
+        <v>0.80436507936507928</v>
+      </c>
+      <c r="D46">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E46" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46">
+        <v>2.5</v>
+      </c>
+      <c r="G46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47">
+        <v>0.59563492063492063</v>
+      </c>
+      <c r="D47">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E47" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47">
+        <v>2.5</v>
+      </c>
+      <c r="G47">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48">
+        <v>0.68492063492063504</v>
+      </c>
+      <c r="D48">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E48" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48">
+        <v>2.5</v>
+      </c>
+      <c r="G48">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <v>0.67738095238095253</v>
+      </c>
+      <c r="D49">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E49" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49">
+        <v>2.5</v>
+      </c>
+      <c r="G49">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50">
+        <v>0.53650793650793649</v>
+      </c>
+      <c r="D50">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E50" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50">
+        <v>2.5</v>
+      </c>
+      <c r="G50">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51">
+        <v>0.69920634920634928</v>
+      </c>
+      <c r="D51">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51">
+        <v>2.5</v>
+      </c>
+      <c r="G51">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52">
+        <v>0.70198412698412704</v>
+      </c>
+      <c r="D52">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E52" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52">
+        <v>2.5</v>
+      </c>
+      <c r="G52">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53">
+        <v>0.61865079365079367</v>
+      </c>
+      <c r="D53">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E53" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53">
+        <v>2.5</v>
+      </c>
+      <c r="G53">
+        <v>30</v>
+      </c>
+      <c r="H53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54">
+        <v>0.67698412698412691</v>
+      </c>
+      <c r="D54">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54">
+        <v>2.5</v>
+      </c>
+      <c r="G54">
+        <v>30</v>
+      </c>
+      <c r="H54" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D55">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55">
+        <v>2.5</v>
+      </c>
+      <c r="G55">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="D56">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E56" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56">
+        <v>2.5</v>
+      </c>
+      <c r="G56">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57">
+        <v>0.74365079365079367</v>
+      </c>
+      <c r="D57">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E57" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57">
+        <v>2.5</v>
+      </c>
+      <c r="G57">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58">
+        <v>0.62063492063492065</v>
+      </c>
+      <c r="D58">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E58" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58">
+        <v>2.5</v>
+      </c>
+      <c r="G58">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59">
+        <v>0.85873015873015879</v>
+      </c>
+      <c r="D59">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E59" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59">
+        <v>2.5</v>
+      </c>
+      <c r="G59">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60">
+        <v>0.75476190476190474</v>
+      </c>
+      <c r="D60">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60">
+        <v>2.5</v>
+      </c>
+      <c r="G60">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61">
+        <v>0.74087301587301591</v>
+      </c>
+      <c r="D61">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E61" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61">
+        <v>2.5</v>
+      </c>
+      <c r="G61">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62">
+        <v>0.67539682539682533</v>
+      </c>
+      <c r="D62">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E62" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62">
+        <v>2.5</v>
+      </c>
+      <c r="G62">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63">
+        <v>0.71507936507936509</v>
+      </c>
+      <c r="D63">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E63" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63">
+        <v>2.5</v>
+      </c>
+      <c r="G63">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64">
+        <v>0.6781746031746031</v>
+      </c>
+      <c r="D64">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E64" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64">
+        <v>2.5</v>
+      </c>
+      <c r="G64">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D65">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E65" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65">
+        <v>2.5</v>
+      </c>
+      <c r="G65">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="D66">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E66" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66">
+        <v>2.5</v>
+      </c>
+      <c r="G66">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67">
+        <v>0.65753968253968254</v>
+      </c>
+      <c r="D67">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E67" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67">
+        <v>2.5</v>
+      </c>
+      <c r="G67">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68">
+        <v>0.66587301587301584</v>
+      </c>
+      <c r="D68">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68">
+        <v>2.5</v>
+      </c>
+      <c r="G68">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69">
+        <v>0.78174603174603174</v>
+      </c>
+      <c r="D69">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E69" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69">
+        <v>2.5</v>
+      </c>
+      <c r="G69">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70">
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="D70">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E70" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70">
+        <v>2.5</v>
+      </c>
+      <c r="G70">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71">
+        <v>0.69444444444444431</v>
+      </c>
+      <c r="D71">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E71" t="s">
+        <v>16</v>
+      </c>
+      <c r="F71">
+        <v>2.5</v>
+      </c>
+      <c r="G71">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72">
+        <v>0.7686507936507937</v>
+      </c>
+      <c r="D72">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E72" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72">
+        <v>2.5</v>
+      </c>
+      <c r="G72">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73">
+        <v>0.61587301587301591</v>
+      </c>
+      <c r="D73">
+        <v>0.34848484848484851</v>
+      </c>
+      <c r="E73" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73">
+        <v>2.5</v>
+      </c>
+      <c r="G73">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74">
+        <v>0.85119047619047628</v>
+      </c>
+      <c r="D74">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74">
+        <v>2.5</v>
+      </c>
+      <c r="G74">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75">
+        <v>0.73809523809523814</v>
+      </c>
+      <c r="D75">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E75" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75">
+        <v>2.5</v>
+      </c>
+      <c r="G75">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76">
+        <v>0.60317460317460325</v>
+      </c>
+      <c r="D76">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E76" t="s">
+        <v>16</v>
+      </c>
+      <c r="F76">
+        <v>2.5</v>
+      </c>
+      <c r="G76">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" t="s">
+        <v>36</v>
+      </c>
+      <c r="C77">
+        <v>0.79642857142857137</v>
+      </c>
+      <c r="D77">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E77" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77">
+        <v>2.5</v>
+      </c>
+      <c r="G77">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" t="s">
+        <v>36</v>
+      </c>
+      <c r="C78">
+        <v>0.68452380952380965</v>
+      </c>
+      <c r="D78">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E78" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78">
+        <v>2.5</v>
+      </c>
+      <c r="G78">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79">
+        <v>0.67738095238095231</v>
+      </c>
+      <c r="D79">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79">
+        <v>2.5</v>
+      </c>
+      <c r="G79">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80">
+        <v>0.81785714285714295</v>
+      </c>
+      <c r="D80">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E80" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80">
+        <v>2.5</v>
+      </c>
+      <c r="G80">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81">
+        <v>0.70198412698412704</v>
+      </c>
+      <c r="D81">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E81" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81">
+        <v>2.5</v>
+      </c>
+      <c r="G81">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82">
+        <v>0.71309523809523812</v>
+      </c>
+      <c r="D82">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E82" t="s">
+        <v>16</v>
+      </c>
+      <c r="F82">
+        <v>2.5</v>
+      </c>
+      <c r="G82">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83">
+        <v>0.66865079365079361</v>
+      </c>
+      <c r="D83">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E83" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83">
+        <v>2.5</v>
+      </c>
+      <c r="G83">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84">
+        <v>0.7325396825396826</v>
+      </c>
+      <c r="D84">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E84" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84">
+        <v>2.5</v>
+      </c>
+      <c r="G84">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" t="s">
+        <v>38</v>
+      </c>
+      <c r="C85">
+        <v>0.68333333333333324</v>
+      </c>
+      <c r="D85">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E85" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85">
+        <v>2.5</v>
+      </c>
+      <c r="G85">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86">
+        <v>0.71706349206349207</v>
+      </c>
+      <c r="D86">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E86" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86">
+        <v>2.5</v>
+      </c>
+      <c r="G86">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B87" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87">
+        <v>0.56031746031746033</v>
+      </c>
+      <c r="D87">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E87" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87">
+        <v>2.5</v>
+      </c>
+      <c r="G87">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88">
+        <v>0.70198412698412704</v>
+      </c>
+      <c r="D88">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88">
+        <v>2.5</v>
+      </c>
+      <c r="G88">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" t="s">
+        <v>40</v>
+      </c>
+      <c r="C89">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="D89">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89">
+        <v>2.5</v>
+      </c>
+      <c r="G89">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90">
+        <v>0.68809523809523798</v>
+      </c>
+      <c r="D90">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E90" t="s">
+        <v>16</v>
+      </c>
+      <c r="F90">
+        <v>2.5</v>
+      </c>
+      <c r="G90">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91">
+        <v>0.81785714285714295</v>
+      </c>
+      <c r="D91">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E91" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91">
+        <v>2.5</v>
+      </c>
+      <c r="G91">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92">
+        <v>0.51944444444444449</v>
+      </c>
+      <c r="D92">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E92" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92">
+        <v>2.5</v>
+      </c>
+      <c r="G92">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93">
+        <v>0.76944444444444449</v>
+      </c>
+      <c r="D93">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E93" t="s">
+        <v>16</v>
+      </c>
+      <c r="F93">
+        <v>2.5</v>
+      </c>
+      <c r="G93">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94">
+        <v>0.68333333333333324</v>
+      </c>
+      <c r="D94">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E94" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94">
+        <v>2.5</v>
+      </c>
+      <c r="G94">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
+        <v>41</v>
+      </c>
+      <c r="C95">
+        <v>0.65753968253968254</v>
+      </c>
+      <c r="D95">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E95" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95">
+        <v>2.5</v>
+      </c>
+      <c r="G95">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="D96">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E96" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96">
+        <v>2.5</v>
+      </c>
+      <c r="G96">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" t="s">
+        <v>33</v>
+      </c>
+      <c r="C97">
+        <v>0.65952380952380951</v>
+      </c>
+      <c r="D97">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E97" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97">
+        <v>2.5</v>
+      </c>
+      <c r="G97">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98">
+        <v>0.7678571428571429</v>
+      </c>
+      <c r="D98">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E98" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98">
+        <v>2.5</v>
+      </c>
+      <c r="G98">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99" t="s">
+        <v>42</v>
+      </c>
+      <c r="C99">
+        <v>0.62341269841269842</v>
+      </c>
+      <c r="D99">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E99" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99">
+        <v>2.5</v>
+      </c>
+      <c r="G99">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C100">
+        <v>0.53253968253968254</v>
+      </c>
+      <c r="D100">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E100" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100">
+        <v>2.5</v>
+      </c>
+      <c r="G100">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="D101">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E101" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101">
+        <v>2.5</v>
+      </c>
+      <c r="G101">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102">
+        <v>0.77182539682539686</v>
+      </c>
+      <c r="D102">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E102" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102">
+        <v>2.5</v>
+      </c>
+      <c r="G102">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" t="s">
+        <v>32</v>
+      </c>
+      <c r="C103">
+        <v>0.71388888888888891</v>
+      </c>
+      <c r="D103">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E103" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103">
+        <v>2.5</v>
+      </c>
+      <c r="G103">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" t="s">
+        <v>34</v>
+      </c>
+      <c r="C104">
+        <v>0.72817460317460314</v>
+      </c>
+      <c r="D104">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E104" t="s">
+        <v>16</v>
+      </c>
+      <c r="F104">
+        <v>2.5</v>
+      </c>
+      <c r="G104">
+        <v>30</v>
+      </c>
+      <c r="H104" t="s">
+        <v>44</v>
+      </c>
+      <c r="I104" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105">
+        <v>0.64880952380952384</v>
+      </c>
+      <c r="D105">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105">
+        <v>2.5</v>
+      </c>
+      <c r="G105">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106" t="s">
+        <v>47</v>
+      </c>
+      <c r="C106">
+        <v>0.68134920634920626</v>
+      </c>
+      <c r="D106">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E106" t="s">
+        <v>16</v>
+      </c>
+      <c r="F106">
+        <v>2.5</v>
+      </c>
+      <c r="G106">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B107" t="s">
         <v>10</v>
       </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19">
-        <v>0.60317460317460325</v>
-      </c>
-      <c r="D19">
+      <c r="C107">
+        <v>0.70436507936507942</v>
+      </c>
+      <c r="D107">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E107" t="s">
+        <v>16</v>
+      </c>
+      <c r="F107">
+        <v>2.5</v>
+      </c>
+      <c r="G107">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B108" t="s">
+        <v>48</v>
+      </c>
+      <c r="C108">
+        <v>0.81349206349206338</v>
+      </c>
+      <c r="D108">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E108" t="s">
+        <v>16</v>
+      </c>
+      <c r="F108">
+        <v>2.5</v>
+      </c>
+      <c r="G108">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B109" t="s">
+        <v>49</v>
+      </c>
+      <c r="C109">
+        <v>0.85198412698412707</v>
+      </c>
+      <c r="D109">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F109">
+        <v>2.5</v>
+      </c>
+      <c r="G109">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110" t="s">
+        <v>50</v>
+      </c>
+      <c r="C110">
+        <v>0.6515873015873016</v>
+      </c>
+      <c r="D110">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E110" t="s">
+        <v>16</v>
+      </c>
+      <c r="F110">
+        <v>2.5</v>
+      </c>
+      <c r="G110">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111" t="s">
+        <v>47</v>
+      </c>
+      <c r="C111">
+        <v>0.62261904761904763</v>
+      </c>
+      <c r="D111">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E111" t="s">
+        <v>16</v>
+      </c>
+      <c r="F111">
+        <v>2.5</v>
+      </c>
+      <c r="G111">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>9</v>
+      </c>
+      <c r="B112" t="s">
+        <v>51</v>
+      </c>
+      <c r="C112">
+        <v>0.70674603174603179</v>
+      </c>
+      <c r="D112">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E112" t="s">
+        <v>16</v>
+      </c>
+      <c r="F112">
+        <v>2.5</v>
+      </c>
+      <c r="G112">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113" t="s">
+        <v>52</v>
+      </c>
+      <c r="C113">
+        <v>0.76071428571428579</v>
+      </c>
+      <c r="D113">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E113" t="s">
+        <v>16</v>
+      </c>
+      <c r="F113">
+        <v>2.5</v>
+      </c>
+      <c r="G113">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>9</v>
+      </c>
+      <c r="B114" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114">
+        <v>0.77539682539682542</v>
+      </c>
+      <c r="D114">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E114" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114">
+        <v>2.5</v>
+      </c>
+      <c r="G114">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>9</v>
+      </c>
+      <c r="B115" t="s">
+        <v>53</v>
+      </c>
+      <c r="C115">
+        <v>0.7496031746031746</v>
+      </c>
+      <c r="D115">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="E115" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115">
+        <v>2.5</v>
+      </c>
+      <c r="G115">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116" t="s">
+        <v>50</v>
+      </c>
+      <c r="C116">
+        <v>0.70793650793650797</v>
+      </c>
+      <c r="D116">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E116" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116">
+        <v>2.5</v>
+      </c>
+      <c r="G116">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>9</v>
+      </c>
+      <c r="B117" t="s">
+        <v>54</v>
+      </c>
+      <c r="C117">
+        <v>0.64920634920634923</v>
+      </c>
+      <c r="D117">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E117" t="s">
+        <v>16</v>
+      </c>
+      <c r="F117">
+        <v>2.5</v>
+      </c>
+      <c r="G117">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>9</v>
+      </c>
+      <c r="B118" t="s">
+        <v>55</v>
+      </c>
+      <c r="C118">
+        <v>0.58015873015873021</v>
+      </c>
+      <c r="D118">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E118" t="s">
+        <v>16</v>
+      </c>
+      <c r="F118">
+        <v>2.5</v>
+      </c>
+      <c r="G118">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>9</v>
+      </c>
+      <c r="B119" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119">
+        <v>0.7146825396825397</v>
+      </c>
+      <c r="D119">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E119" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119">
+        <v>2.5</v>
+      </c>
+      <c r="G119">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>9</v>
+      </c>
+      <c r="B120" t="s">
+        <v>57</v>
+      </c>
+      <c r="C120">
+        <v>0.72619047619047628</v>
+      </c>
+      <c r="D120">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E120" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120">
+        <v>2.5</v>
+      </c>
+      <c r="G120">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>9</v>
+      </c>
+      <c r="B121" t="s">
+        <v>58</v>
+      </c>
+      <c r="C121">
+        <v>0.62777777777777777</v>
+      </c>
+      <c r="D121">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E121" t="s">
+        <v>16</v>
+      </c>
+      <c r="F121">
+        <v>2.5</v>
+      </c>
+      <c r="G121">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>9</v>
+      </c>
+      <c r="B122" t="s">
+        <v>51</v>
+      </c>
+      <c r="C122">
+        <v>0.78134920634920635</v>
+      </c>
+      <c r="D122">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E122" t="s">
+        <v>16</v>
+      </c>
+      <c r="F122">
+        <v>2.5</v>
+      </c>
+      <c r="G122">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>9</v>
+      </c>
+      <c r="B123" t="s">
+        <v>59</v>
+      </c>
+      <c r="C123">
+        <v>0.69920634920634928</v>
+      </c>
+      <c r="D123">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E123" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123">
+        <v>2.5</v>
+      </c>
+      <c r="G123">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>9</v>
+      </c>
+      <c r="B124" t="s">
+        <v>58</v>
+      </c>
+      <c r="C124">
+        <v>0.79325396825396821</v>
+      </c>
+      <c r="D124">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124">
+        <v>2.5</v>
+      </c>
+      <c r="G124">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125" t="s">
+        <v>60</v>
+      </c>
+      <c r="C125">
+        <v>0.58611111111111114</v>
+      </c>
+      <c r="D125">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E125" t="s">
+        <v>16</v>
+      </c>
+      <c r="F125">
+        <v>2.5</v>
+      </c>
+      <c r="G125">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126" t="s">
+        <v>61</v>
+      </c>
+      <c r="C126">
+        <v>0.65396825396825387</v>
+      </c>
+      <c r="D126">
         <v>0.5757575757575758</v>
       </c>
-      <c r="E19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>150</v>
+      <c r="E126" t="s">
+        <v>16</v>
+      </c>
+      <c r="F126">
+        <v>2.5</v>
+      </c>
+      <c r="G126">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>9</v>
+      </c>
+      <c r="B127" t="s">
+        <v>62</v>
+      </c>
+      <c r="C127">
+        <v>0.77261904761904765</v>
+      </c>
+      <c r="D127">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E127" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127">
+        <v>2.5</v>
+      </c>
+      <c r="G127">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>9</v>
+      </c>
+      <c r="B128" t="s">
+        <v>63</v>
+      </c>
+      <c r="C128">
+        <v>0.68730158730158719</v>
+      </c>
+      <c r="D128">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E128" t="s">
+        <v>16</v>
+      </c>
+      <c r="F128">
+        <v>2.5</v>
+      </c>
+      <c r="G128">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129" t="s">
+        <v>64</v>
+      </c>
+      <c r="C129">
+        <v>0.6603174603174603</v>
+      </c>
+      <c r="D129">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E129" t="s">
+        <v>16</v>
+      </c>
+      <c r="F129">
+        <v>2.5</v>
+      </c>
+      <c r="G129">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>9</v>
+      </c>
+      <c r="B130" t="s">
+        <v>46</v>
+      </c>
+      <c r="C130">
+        <v>0.57579365079365086</v>
+      </c>
+      <c r="D130">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E130" t="s">
+        <v>16</v>
+      </c>
+      <c r="F130">
+        <v>2.5</v>
+      </c>
+      <c r="G130">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131" t="s">
+        <v>65</v>
+      </c>
+      <c r="C131">
+        <v>0.69007936507936518</v>
+      </c>
+      <c r="D131">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E131" t="s">
+        <v>16</v>
+      </c>
+      <c r="F131">
+        <v>2.5</v>
+      </c>
+      <c r="G131">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>9</v>
+      </c>
+      <c r="B132" t="s">
+        <v>66</v>
+      </c>
+      <c r="C132">
+        <v>0.64682539682539675</v>
+      </c>
+      <c r="D132">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E132" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132">
+        <v>2.5</v>
+      </c>
+      <c r="G132">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133" t="s">
+        <v>67</v>
+      </c>
+      <c r="C133">
+        <v>0.68611111111111123</v>
+      </c>
+      <c r="D133">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E133" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133">
+        <v>2.5</v>
+      </c>
+      <c r="G133">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134" t="s">
+        <v>66</v>
+      </c>
+      <c r="C134">
+        <v>0.72698412698412707</v>
+      </c>
+      <c r="D134">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134">
+        <v>2.5</v>
+      </c>
+      <c r="G134">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135" t="s">
+        <v>10</v>
+      </c>
+      <c r="C135">
+        <v>0.75079365079365079</v>
+      </c>
+      <c r="D135">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E135" t="s">
+        <v>16</v>
+      </c>
+      <c r="F135">
+        <v>2.5</v>
+      </c>
+      <c r="G135">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>9</v>
+      </c>
+      <c r="B136" t="s">
+        <v>67</v>
+      </c>
+      <c r="C136">
+        <v>0.67539682539682533</v>
+      </c>
+      <c r="D136">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E136" t="s">
+        <v>16</v>
+      </c>
+      <c r="F136">
+        <v>2.5</v>
+      </c>
+      <c r="G136">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137" t="s">
+        <v>68</v>
+      </c>
+      <c r="C137">
+        <v>0.71706349206349207</v>
+      </c>
+      <c r="D137">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E137" t="s">
+        <v>16</v>
+      </c>
+      <c r="F137">
+        <v>2.5</v>
+      </c>
+      <c r="G137">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" t="s">
+        <v>69</v>
+      </c>
+      <c r="C138">
+        <v>0.76349206349206344</v>
+      </c>
+      <c r="D138">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E138" t="s">
+        <v>16</v>
+      </c>
+      <c r="F138">
+        <v>2.5</v>
+      </c>
+      <c r="G138">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" t="s">
+        <v>70</v>
+      </c>
+      <c r="C139">
+        <v>0.80039682539682533</v>
+      </c>
+      <c r="D139">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E139" t="s">
+        <v>16</v>
+      </c>
+      <c r="F139">
+        <v>2.5</v>
+      </c>
+      <c r="G139">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" t="s">
+        <v>71</v>
+      </c>
+      <c r="C140">
+        <v>0.6253968253968254</v>
+      </c>
+      <c r="D140">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E140" t="s">
+        <v>16</v>
+      </c>
+      <c r="F140">
+        <v>2.5</v>
+      </c>
+      <c r="G140">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141" t="s">
+        <v>67</v>
+      </c>
+      <c r="C141">
+        <v>0.75396825396825395</v>
+      </c>
+      <c r="D141">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E141" t="s">
+        <v>16</v>
+      </c>
+      <c r="F141">
+        <v>2.5</v>
+      </c>
+      <c r="G141">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142" t="s">
+        <v>59</v>
+      </c>
+      <c r="C142">
+        <v>0.68809523809523798</v>
+      </c>
+      <c r="D142">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E142" t="s">
+        <v>16</v>
+      </c>
+      <c r="F142">
+        <v>2.5</v>
+      </c>
+      <c r="G142">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143" t="s">
+        <v>72</v>
+      </c>
+      <c r="C143">
+        <v>0.82301587301587309</v>
+      </c>
+      <c r="D143">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E143" t="s">
+        <v>16</v>
+      </c>
+      <c r="F143">
+        <v>2.5</v>
+      </c>
+      <c r="G143">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144" t="s">
+        <v>73</v>
+      </c>
+      <c r="C144">
+        <v>0.67182539682539699</v>
+      </c>
+      <c r="D144">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E144" t="s">
+        <v>16</v>
+      </c>
+      <c r="F144">
+        <v>2.5</v>
+      </c>
+      <c r="G144">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" t="s">
+        <v>57</v>
+      </c>
+      <c r="C145">
+        <v>0.61230158730158735</v>
+      </c>
+      <c r="D145">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E145" t="s">
+        <v>16</v>
+      </c>
+      <c r="F145">
+        <v>2.5</v>
+      </c>
+      <c r="G145">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" t="s">
+        <v>74</v>
+      </c>
+      <c r="C146">
+        <v>0.81269841269841281</v>
+      </c>
+      <c r="D146">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E146" t="s">
+        <v>16</v>
+      </c>
+      <c r="F146">
+        <v>2.5</v>
+      </c>
+      <c r="G146">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147" t="s">
+        <v>64</v>
+      </c>
+      <c r="C147">
+        <v>0.65515873015873016</v>
+      </c>
+      <c r="D147">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E147" t="s">
+        <v>16</v>
+      </c>
+      <c r="F147">
+        <v>2.5</v>
+      </c>
+      <c r="G147">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" t="s">
+        <v>55</v>
+      </c>
+      <c r="C148">
+        <v>0.80753968253968245</v>
+      </c>
+      <c r="D148">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E148" t="s">
+        <v>16</v>
+      </c>
+      <c r="F148">
+        <v>2.5</v>
+      </c>
+      <c r="G148">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149" t="s">
+        <v>75</v>
+      </c>
+      <c r="C149">
+        <v>0.71269841269841272</v>
+      </c>
+      <c r="D149">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E149" t="s">
+        <v>16</v>
+      </c>
+      <c r="F149">
+        <v>2.5</v>
+      </c>
+      <c r="G149">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150" t="s">
+        <v>61</v>
+      </c>
+      <c r="C150">
+        <v>0.65436507936507937</v>
+      </c>
+      <c r="D150">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E150" t="s">
+        <v>16</v>
+      </c>
+      <c r="F150">
+        <v>2.5</v>
+      </c>
+      <c r="G150">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151" t="s">
+        <v>53</v>
+      </c>
+      <c r="C151">
+        <v>0.74563492063492065</v>
+      </c>
+      <c r="D151">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E151" t="s">
+        <v>16</v>
+      </c>
+      <c r="F151">
+        <v>2.5</v>
+      </c>
+      <c r="G151">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" t="s">
+        <v>66</v>
+      </c>
+      <c r="C152">
+        <v>0.80833333333333324</v>
+      </c>
+      <c r="D152">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E152" t="s">
+        <v>16</v>
+      </c>
+      <c r="F152">
+        <v>2.5</v>
+      </c>
+      <c r="G152">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153" t="s">
+        <v>69</v>
+      </c>
+      <c r="C153">
+        <v>0.6337301587301587</v>
+      </c>
+      <c r="D153">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E153" t="s">
+        <v>16</v>
+      </c>
+      <c r="F153">
+        <v>2.5</v>
+      </c>
+      <c r="G153">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154" t="s">
+        <v>46</v>
+      </c>
+      <c r="C154">
+        <v>0.76071428571428568</v>
+      </c>
+      <c r="D154">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E154" t="s">
+        <v>16</v>
+      </c>
+      <c r="F154">
+        <v>2.5</v>
+      </c>
+      <c r="G154">
+        <v>30</v>
+      </c>
+      <c r="H154" t="s">
+        <v>76</v>
+      </c>
+      <c r="I154" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_1EE9D7F4136D540F62355476585DCE3A87468CB8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC52B072-223B-44A9-AAE2-D0032DDA15BC}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_49B9D71E964C440E62355476585DCE3A87458BAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8333085E-90FA-4C27-9545-504AB8F6BB04}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="106">
   <si>
     <t>Model</t>
   </si>
@@ -254,6 +254,90 @@
   </si>
   <si>
     <t>0.1700</t>
+  </si>
+  <si>
+    <t>0.7415</t>
+  </si>
+  <si>
+    <t>0.1322</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 10, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 5, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>0.6476</t>
+  </si>
+  <si>
+    <t>0.1319</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>0.6752</t>
+  </si>
+  <si>
+    <t>0.1636</t>
   </si>
 </sst>
 </file>
@@ -616,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I304"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -4191,6 +4275,3474 @@
         <v>77</v>
       </c>
     </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>14</v>
+      </c>
+      <c r="B155" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155">
+        <v>0.69841269841269848</v>
+      </c>
+      <c r="D155">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E155" t="s">
+        <v>16</v>
+      </c>
+      <c r="F155">
+        <v>2.5</v>
+      </c>
+      <c r="G155">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" t="s">
+        <v>15</v>
+      </c>
+      <c r="C156">
+        <v>0.69523809523809532</v>
+      </c>
+      <c r="D156">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E156" t="s">
+        <v>16</v>
+      </c>
+      <c r="F156">
+        <v>2.5</v>
+      </c>
+      <c r="G156">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>14</v>
+      </c>
+      <c r="B157" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157">
+        <v>0.70714285714285718</v>
+      </c>
+      <c r="D157">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E157" t="s">
+        <v>16</v>
+      </c>
+      <c r="F157">
+        <v>2.5</v>
+      </c>
+      <c r="G157">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>14</v>
+      </c>
+      <c r="B158" t="s">
+        <v>15</v>
+      </c>
+      <c r="C158">
+        <v>0.57579365079365075</v>
+      </c>
+      <c r="D158">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E158" t="s">
+        <v>16</v>
+      </c>
+      <c r="F158">
+        <v>2.5</v>
+      </c>
+      <c r="G158">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>14</v>
+      </c>
+      <c r="B159" t="s">
+        <v>15</v>
+      </c>
+      <c r="C159">
+        <v>0.68888888888888877</v>
+      </c>
+      <c r="D159">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E159" t="s">
+        <v>16</v>
+      </c>
+      <c r="F159">
+        <v>2.5</v>
+      </c>
+      <c r="G159">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>14</v>
+      </c>
+      <c r="B160" t="s">
+        <v>15</v>
+      </c>
+      <c r="C160">
+        <v>0.598015873015873</v>
+      </c>
+      <c r="D160">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E160" t="s">
+        <v>16</v>
+      </c>
+      <c r="F160">
+        <v>2.5</v>
+      </c>
+      <c r="G160">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>14</v>
+      </c>
+      <c r="B161" t="s">
+        <v>15</v>
+      </c>
+      <c r="C161">
+        <v>0.57817460317460323</v>
+      </c>
+      <c r="D161">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E161" t="s">
+        <v>16</v>
+      </c>
+      <c r="F161">
+        <v>2.5</v>
+      </c>
+      <c r="G161">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>14</v>
+      </c>
+      <c r="B162" t="s">
+        <v>15</v>
+      </c>
+      <c r="C162">
+        <v>0.74404761904761907</v>
+      </c>
+      <c r="D162">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E162" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162">
+        <v>2.5</v>
+      </c>
+      <c r="G162">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>14</v>
+      </c>
+      <c r="B163" t="s">
+        <v>15</v>
+      </c>
+      <c r="C163">
+        <v>0.58769841269841272</v>
+      </c>
+      <c r="D163">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E163" t="s">
+        <v>16</v>
+      </c>
+      <c r="F163">
+        <v>2.5</v>
+      </c>
+      <c r="G163">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="D164">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E164" t="s">
+        <v>16</v>
+      </c>
+      <c r="F164">
+        <v>2.5</v>
+      </c>
+      <c r="G164">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>14</v>
+      </c>
+      <c r="B165" t="s">
+        <v>15</v>
+      </c>
+      <c r="C165">
+        <v>0.50436507936507935</v>
+      </c>
+      <c r="D165">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E165" t="s">
+        <v>16</v>
+      </c>
+      <c r="F165">
+        <v>2.5</v>
+      </c>
+      <c r="G165">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>14</v>
+      </c>
+      <c r="B166" t="s">
+        <v>15</v>
+      </c>
+      <c r="C166">
+        <v>0.81904761904761914</v>
+      </c>
+      <c r="D166">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E166" t="s">
+        <v>16</v>
+      </c>
+      <c r="F166">
+        <v>2.5</v>
+      </c>
+      <c r="G166">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" t="s">
+        <v>15</v>
+      </c>
+      <c r="C167">
+        <v>0.57500000000000007</v>
+      </c>
+      <c r="D167">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E167" t="s">
+        <v>16</v>
+      </c>
+      <c r="F167">
+        <v>2.5</v>
+      </c>
+      <c r="G167">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>14</v>
+      </c>
+      <c r="B168" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168">
+        <v>0.62896825396825395</v>
+      </c>
+      <c r="D168">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E168" t="s">
+        <v>16</v>
+      </c>
+      <c r="F168">
+        <v>2.5</v>
+      </c>
+      <c r="G168">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>14</v>
+      </c>
+      <c r="B169" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169">
+        <v>0.80992063492063482</v>
+      </c>
+      <c r="D169">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E169" t="s">
+        <v>16</v>
+      </c>
+      <c r="F169">
+        <v>2.5</v>
+      </c>
+      <c r="G169">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170">
+        <v>0.60238095238095235</v>
+      </c>
+      <c r="D170">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E170" t="s">
+        <v>16</v>
+      </c>
+      <c r="F170">
+        <v>2.5</v>
+      </c>
+      <c r="G170">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>14</v>
+      </c>
+      <c r="B171" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171">
+        <v>0.71785714285714286</v>
+      </c>
+      <c r="D171">
+        <v>0.34848484848484851</v>
+      </c>
+      <c r="E171" t="s">
+        <v>16</v>
+      </c>
+      <c r="F171">
+        <v>2.5</v>
+      </c>
+      <c r="G171">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>14</v>
+      </c>
+      <c r="B172" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172">
+        <v>0.71190476190476193</v>
+      </c>
+      <c r="D172">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E172" t="s">
+        <v>16</v>
+      </c>
+      <c r="F172">
+        <v>2.5</v>
+      </c>
+      <c r="G172">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173">
+        <v>0.7146825396825397</v>
+      </c>
+      <c r="D173">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E173" t="s">
+        <v>16</v>
+      </c>
+      <c r="F173">
+        <v>2.5</v>
+      </c>
+      <c r="G173">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>14</v>
+      </c>
+      <c r="B174" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174">
+        <v>0.74642857142857133</v>
+      </c>
+      <c r="D174">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E174" t="s">
+        <v>16</v>
+      </c>
+      <c r="F174">
+        <v>2.5</v>
+      </c>
+      <c r="G174">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>14</v>
+      </c>
+      <c r="B175" t="s">
+        <v>15</v>
+      </c>
+      <c r="C175">
+        <v>0.71984126984126995</v>
+      </c>
+      <c r="D175">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E175" t="s">
+        <v>16</v>
+      </c>
+      <c r="F175">
+        <v>2.5</v>
+      </c>
+      <c r="G175">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>14</v>
+      </c>
+      <c r="B176" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176">
+        <v>0.58650793650793653</v>
+      </c>
+      <c r="D176">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E176" t="s">
+        <v>16</v>
+      </c>
+      <c r="F176">
+        <v>2.5</v>
+      </c>
+      <c r="G176">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>14</v>
+      </c>
+      <c r="B177" t="s">
+        <v>15</v>
+      </c>
+      <c r="C177">
+        <v>0.71746031746031758</v>
+      </c>
+      <c r="D177">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E177" t="s">
+        <v>16</v>
+      </c>
+      <c r="F177">
+        <v>2.5</v>
+      </c>
+      <c r="G177">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>14</v>
+      </c>
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178">
+        <v>0.70158730158730165</v>
+      </c>
+      <c r="D178">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E178" t="s">
+        <v>16</v>
+      </c>
+      <c r="F178">
+        <v>2.5</v>
+      </c>
+      <c r="G178">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>14</v>
+      </c>
+      <c r="B179" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179">
+        <v>0.76904761904761898</v>
+      </c>
+      <c r="D179">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E179" t="s">
+        <v>16</v>
+      </c>
+      <c r="F179">
+        <v>2.5</v>
+      </c>
+      <c r="G179">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>14</v>
+      </c>
+      <c r="B180" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180">
+        <v>0.69960317460317467</v>
+      </c>
+      <c r="D180">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E180" t="s">
+        <v>16</v>
+      </c>
+      <c r="F180">
+        <v>2.5</v>
+      </c>
+      <c r="G180">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>14</v>
+      </c>
+      <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181">
+        <v>0.6432539682539683</v>
+      </c>
+      <c r="D181">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E181" t="s">
+        <v>16</v>
+      </c>
+      <c r="F181">
+        <v>2.5</v>
+      </c>
+      <c r="G181">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>14</v>
+      </c>
+      <c r="B182" t="s">
+        <v>15</v>
+      </c>
+      <c r="C182">
+        <v>0.71547619047619049</v>
+      </c>
+      <c r="D182">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E182" t="s">
+        <v>16</v>
+      </c>
+      <c r="F182">
+        <v>2.5</v>
+      </c>
+      <c r="G182">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>14</v>
+      </c>
+      <c r="B183" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183">
+        <v>0.776984126984127</v>
+      </c>
+      <c r="D183">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E183" t="s">
+        <v>16</v>
+      </c>
+      <c r="F183">
+        <v>2.5</v>
+      </c>
+      <c r="G183">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>14</v>
+      </c>
+      <c r="B184" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184">
+        <v>0.85873015873015868</v>
+      </c>
+      <c r="D184">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E184" t="s">
+        <v>16</v>
+      </c>
+      <c r="F184">
+        <v>2.5</v>
+      </c>
+      <c r="G184">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>14</v>
+      </c>
+      <c r="B185" t="s">
+        <v>15</v>
+      </c>
+      <c r="C185">
+        <v>0.77619047619047621</v>
+      </c>
+      <c r="D185">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E185" t="s">
+        <v>16</v>
+      </c>
+      <c r="F185">
+        <v>2.5</v>
+      </c>
+      <c r="G185">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>14</v>
+      </c>
+      <c r="B186" t="s">
+        <v>15</v>
+      </c>
+      <c r="C186">
+        <v>0.64960317460317463</v>
+      </c>
+      <c r="D186">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E186" t="s">
+        <v>16</v>
+      </c>
+      <c r="F186">
+        <v>2.5</v>
+      </c>
+      <c r="G186">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" t="s">
+        <v>15</v>
+      </c>
+      <c r="C187">
+        <v>0.56706349206349216</v>
+      </c>
+      <c r="D187">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E187" t="s">
+        <v>16</v>
+      </c>
+      <c r="F187">
+        <v>2.5</v>
+      </c>
+      <c r="G187">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>14</v>
+      </c>
+      <c r="B188" t="s">
+        <v>15</v>
+      </c>
+      <c r="C188">
+        <v>0.83373015873015877</v>
+      </c>
+      <c r="D188">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E188" t="s">
+        <v>16</v>
+      </c>
+      <c r="F188">
+        <v>2.5</v>
+      </c>
+      <c r="G188">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>14</v>
+      </c>
+      <c r="B189" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189">
+        <v>0.72936507936507944</v>
+      </c>
+      <c r="D189">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E189" t="s">
+        <v>16</v>
+      </c>
+      <c r="F189">
+        <v>2.5</v>
+      </c>
+      <c r="G189">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>14</v>
+      </c>
+      <c r="B190" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190">
+        <v>0.73849206349206353</v>
+      </c>
+      <c r="D190">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E190" t="s">
+        <v>16</v>
+      </c>
+      <c r="F190">
+        <v>2.5</v>
+      </c>
+      <c r="G190">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>14</v>
+      </c>
+      <c r="B191" t="s">
+        <v>15</v>
+      </c>
+      <c r="C191">
+        <v>0.70873015873015888</v>
+      </c>
+      <c r="D191">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E191" t="s">
+        <v>16</v>
+      </c>
+      <c r="F191">
+        <v>2.5</v>
+      </c>
+      <c r="G191">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>14</v>
+      </c>
+      <c r="B192" t="s">
+        <v>15</v>
+      </c>
+      <c r="C192">
+        <v>0.56428571428571439</v>
+      </c>
+      <c r="D192">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E192" t="s">
+        <v>16</v>
+      </c>
+      <c r="F192">
+        <v>2.5</v>
+      </c>
+      <c r="G192">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>14</v>
+      </c>
+      <c r="B193" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193">
+        <v>0.68571428571428561</v>
+      </c>
+      <c r="D193">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E193" t="s">
+        <v>16</v>
+      </c>
+      <c r="F193">
+        <v>2.5</v>
+      </c>
+      <c r="G193">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" t="s">
+        <v>15</v>
+      </c>
+      <c r="C194">
+        <v>0.63650793650793647</v>
+      </c>
+      <c r="D194">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E194" t="s">
+        <v>16</v>
+      </c>
+      <c r="F194">
+        <v>2.5</v>
+      </c>
+      <c r="G194">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>14</v>
+      </c>
+      <c r="B195" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195">
+        <v>0.71269841269841272</v>
+      </c>
+      <c r="D195">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E195" t="s">
+        <v>16</v>
+      </c>
+      <c r="F195">
+        <v>2.5</v>
+      </c>
+      <c r="G195">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>14</v>
+      </c>
+      <c r="B196" t="s">
+        <v>15</v>
+      </c>
+      <c r="C196">
+        <v>0.81626984126984115</v>
+      </c>
+      <c r="D196">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E196" t="s">
+        <v>16</v>
+      </c>
+      <c r="F196">
+        <v>2.5</v>
+      </c>
+      <c r="G196">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>14</v>
+      </c>
+      <c r="B197" t="s">
+        <v>15</v>
+      </c>
+      <c r="C197">
+        <v>0.59642857142857142</v>
+      </c>
+      <c r="D197">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E197" t="s">
+        <v>16</v>
+      </c>
+      <c r="F197">
+        <v>2.5</v>
+      </c>
+      <c r="G197">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>14</v>
+      </c>
+      <c r="B198" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198">
+        <v>0.68492063492063504</v>
+      </c>
+      <c r="D198">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E198" t="s">
+        <v>16</v>
+      </c>
+      <c r="F198">
+        <v>2.5</v>
+      </c>
+      <c r="G198">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199">
+        <v>0.63293650793650791</v>
+      </c>
+      <c r="D199">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E199" t="s">
+        <v>16</v>
+      </c>
+      <c r="F199">
+        <v>2.5</v>
+      </c>
+      <c r="G199">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200">
+        <v>0.55873015873015863</v>
+      </c>
+      <c r="D200">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E200" t="s">
+        <v>16</v>
+      </c>
+      <c r="F200">
+        <v>2.5</v>
+      </c>
+      <c r="G200">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>14</v>
+      </c>
+      <c r="B201" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201">
+        <v>0.79642857142857137</v>
+      </c>
+      <c r="D201">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E201" t="s">
+        <v>16</v>
+      </c>
+      <c r="F201">
+        <v>2.5</v>
+      </c>
+      <c r="G201">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202">
+        <v>0.70119047619047625</v>
+      </c>
+      <c r="D202">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E202" t="s">
+        <v>16</v>
+      </c>
+      <c r="F202">
+        <v>2.5</v>
+      </c>
+      <c r="G202">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>14</v>
+      </c>
+      <c r="B203" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203">
+        <v>0.69007936507936518</v>
+      </c>
+      <c r="D203">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E203" t="s">
+        <v>16</v>
+      </c>
+      <c r="F203">
+        <v>2.5</v>
+      </c>
+      <c r="G203">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>14</v>
+      </c>
+      <c r="B204" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204">
+        <v>0.67698412698412691</v>
+      </c>
+      <c r="D204">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E204" t="s">
+        <v>16</v>
+      </c>
+      <c r="F204">
+        <v>2.5</v>
+      </c>
+      <c r="G204">
+        <v>20</v>
+      </c>
+      <c r="H204" t="s">
+        <v>78</v>
+      </c>
+      <c r="I204" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>12</v>
+      </c>
+      <c r="B205" t="s">
+        <v>38</v>
+      </c>
+      <c r="C205">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D205">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E205" t="s">
+        <v>16</v>
+      </c>
+      <c r="F205">
+        <v>2.5</v>
+      </c>
+      <c r="G205">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>12</v>
+      </c>
+      <c r="B206" t="s">
+        <v>37</v>
+      </c>
+      <c r="C206">
+        <v>0.75277777777777777</v>
+      </c>
+      <c r="D206">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E206" t="s">
+        <v>16</v>
+      </c>
+      <c r="F206">
+        <v>2.5</v>
+      </c>
+      <c r="G206">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>12</v>
+      </c>
+      <c r="B207" t="s">
+        <v>80</v>
+      </c>
+      <c r="C207">
+        <v>0.73174603174603181</v>
+      </c>
+      <c r="D207">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E207" t="s">
+        <v>16</v>
+      </c>
+      <c r="F207">
+        <v>2.5</v>
+      </c>
+      <c r="G207">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>12</v>
+      </c>
+      <c r="B208" t="s">
+        <v>30</v>
+      </c>
+      <c r="C208">
+        <v>0.61507936507936511</v>
+      </c>
+      <c r="D208">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E208" t="s">
+        <v>16</v>
+      </c>
+      <c r="F208">
+        <v>2.5</v>
+      </c>
+      <c r="G208">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>12</v>
+      </c>
+      <c r="B209" t="s">
+        <v>25</v>
+      </c>
+      <c r="C209">
+        <v>0.84563492063492074</v>
+      </c>
+      <c r="D209">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E209" t="s">
+        <v>16</v>
+      </c>
+      <c r="F209">
+        <v>2.5</v>
+      </c>
+      <c r="G209">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>12</v>
+      </c>
+      <c r="B210" t="s">
+        <v>26</v>
+      </c>
+      <c r="C210">
+        <v>0.72063492063492074</v>
+      </c>
+      <c r="D210">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E210" t="s">
+        <v>16</v>
+      </c>
+      <c r="F210">
+        <v>2.5</v>
+      </c>
+      <c r="G210">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>12</v>
+      </c>
+      <c r="B211" t="s">
+        <v>38</v>
+      </c>
+      <c r="C211">
+        <v>0.70674603174603179</v>
+      </c>
+      <c r="D211">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E211" t="s">
+        <v>16</v>
+      </c>
+      <c r="F211">
+        <v>2.5</v>
+      </c>
+      <c r="G211">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>12</v>
+      </c>
+      <c r="B212" t="s">
+        <v>24</v>
+      </c>
+      <c r="C212">
+        <v>0.6337301587301587</v>
+      </c>
+      <c r="D212">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E212" t="s">
+        <v>16</v>
+      </c>
+      <c r="F212">
+        <v>2.5</v>
+      </c>
+      <c r="G212">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>12</v>
+      </c>
+      <c r="B213" t="s">
+        <v>34</v>
+      </c>
+      <c r="C213">
+        <v>0.67063492063492058</v>
+      </c>
+      <c r="D213">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E213" t="s">
+        <v>16</v>
+      </c>
+      <c r="F213">
+        <v>2.5</v>
+      </c>
+      <c r="G213">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>12</v>
+      </c>
+      <c r="B214" t="s">
+        <v>81</v>
+      </c>
+      <c r="C214">
+        <v>0.71031746031746035</v>
+      </c>
+      <c r="D214">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E214" t="s">
+        <v>16</v>
+      </c>
+      <c r="F214">
+        <v>2.5</v>
+      </c>
+      <c r="G214">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>12</v>
+      </c>
+      <c r="B215" t="s">
+        <v>40</v>
+      </c>
+      <c r="C215">
+        <v>0.61587301587301591</v>
+      </c>
+      <c r="D215">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E215" t="s">
+        <v>16</v>
+      </c>
+      <c r="F215">
+        <v>2.5</v>
+      </c>
+      <c r="G215">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>12</v>
+      </c>
+      <c r="B216" t="s">
+        <v>42</v>
+      </c>
+      <c r="C216">
+        <v>0.73888888888888893</v>
+      </c>
+      <c r="D216">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E216" t="s">
+        <v>16</v>
+      </c>
+      <c r="F216">
+        <v>2.5</v>
+      </c>
+      <c r="G216">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>12</v>
+      </c>
+      <c r="B217" t="s">
+        <v>24</v>
+      </c>
+      <c r="C217">
+        <v>0.65753968253968254</v>
+      </c>
+      <c r="D217">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E217" t="s">
+        <v>16</v>
+      </c>
+      <c r="F217">
+        <v>2.5</v>
+      </c>
+      <c r="G217">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>12</v>
+      </c>
+      <c r="B218" t="s">
+        <v>32</v>
+      </c>
+      <c r="C218">
+        <v>0.64642857142857146</v>
+      </c>
+      <c r="D218">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E218" t="s">
+        <v>16</v>
+      </c>
+      <c r="F218">
+        <v>2.5</v>
+      </c>
+      <c r="G218">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>12</v>
+      </c>
+      <c r="B219" t="s">
+        <v>24</v>
+      </c>
+      <c r="C219">
+        <v>0.87896825396825395</v>
+      </c>
+      <c r="D219">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E219" t="s">
+        <v>16</v>
+      </c>
+      <c r="F219">
+        <v>2.5</v>
+      </c>
+      <c r="G219">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>12</v>
+      </c>
+      <c r="B220" t="s">
+        <v>23</v>
+      </c>
+      <c r="C220">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D220">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E220" t="s">
+        <v>16</v>
+      </c>
+      <c r="F220">
+        <v>2.5</v>
+      </c>
+      <c r="G220">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>12</v>
+      </c>
+      <c r="B221" t="s">
+        <v>24</v>
+      </c>
+      <c r="C221">
+        <v>0.75</v>
+      </c>
+      <c r="D221">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E221" t="s">
+        <v>16</v>
+      </c>
+      <c r="F221">
+        <v>2.5</v>
+      </c>
+      <c r="G221">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222" t="s">
+        <v>24</v>
+      </c>
+      <c r="C222">
+        <v>0.77063492063492056</v>
+      </c>
+      <c r="D222">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E222" t="s">
+        <v>16</v>
+      </c>
+      <c r="F222">
+        <v>2.5</v>
+      </c>
+      <c r="G222">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>12</v>
+      </c>
+      <c r="B223" t="s">
+        <v>21</v>
+      </c>
+      <c r="C223">
+        <v>0.68730158730158741</v>
+      </c>
+      <c r="D223">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E223" t="s">
+        <v>16</v>
+      </c>
+      <c r="F223">
+        <v>2.5</v>
+      </c>
+      <c r="G223">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>12</v>
+      </c>
+      <c r="B224" t="s">
+        <v>21</v>
+      </c>
+      <c r="C224">
+        <v>0.79761904761904756</v>
+      </c>
+      <c r="D224">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E224" t="s">
+        <v>16</v>
+      </c>
+      <c r="F224">
+        <v>2.5</v>
+      </c>
+      <c r="G224">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>12</v>
+      </c>
+      <c r="B225" t="s">
+        <v>21</v>
+      </c>
+      <c r="C225">
+        <v>0.72698412698412707</v>
+      </c>
+      <c r="D225">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E225" t="s">
+        <v>16</v>
+      </c>
+      <c r="F225">
+        <v>2.5</v>
+      </c>
+      <c r="G225">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>12</v>
+      </c>
+      <c r="B226" t="s">
+        <v>33</v>
+      </c>
+      <c r="C226">
+        <v>0.67063492063492058</v>
+      </c>
+      <c r="D226">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E226" t="s">
+        <v>16</v>
+      </c>
+      <c r="F226">
+        <v>2.5</v>
+      </c>
+      <c r="G226">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" t="s">
+        <v>21</v>
+      </c>
+      <c r="C227">
+        <v>0.75476190476190474</v>
+      </c>
+      <c r="D227">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E227" t="s">
+        <v>16</v>
+      </c>
+      <c r="F227">
+        <v>2.5</v>
+      </c>
+      <c r="G227">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228" t="s">
+        <v>13</v>
+      </c>
+      <c r="C228">
+        <v>0.705952380952381</v>
+      </c>
+      <c r="D228">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E228" t="s">
+        <v>16</v>
+      </c>
+      <c r="F228">
+        <v>2.5</v>
+      </c>
+      <c r="G228">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>12</v>
+      </c>
+      <c r="B229" t="s">
+        <v>37</v>
+      </c>
+      <c r="C229">
+        <v>0.66626984126984123</v>
+      </c>
+      <c r="D229">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E229" t="s">
+        <v>16</v>
+      </c>
+      <c r="F229">
+        <v>2.5</v>
+      </c>
+      <c r="G229">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>12</v>
+      </c>
+      <c r="B230" t="s">
+        <v>82</v>
+      </c>
+      <c r="C230">
+        <v>0.71587301587301599</v>
+      </c>
+      <c r="D230">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E230" t="s">
+        <v>16</v>
+      </c>
+      <c r="F230">
+        <v>2.5</v>
+      </c>
+      <c r="G230">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>12</v>
+      </c>
+      <c r="B231" t="s">
+        <v>83</v>
+      </c>
+      <c r="C231">
+        <v>0.71309523809523812</v>
+      </c>
+      <c r="D231">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E231" t="s">
+        <v>16</v>
+      </c>
+      <c r="F231">
+        <v>2.5</v>
+      </c>
+      <c r="G231">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>12</v>
+      </c>
+      <c r="B232" t="s">
+        <v>40</v>
+      </c>
+      <c r="C232">
+        <v>0.67142857142857137</v>
+      </c>
+      <c r="D232">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E232" t="s">
+        <v>16</v>
+      </c>
+      <c r="F232">
+        <v>2.5</v>
+      </c>
+      <c r="G232">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>12</v>
+      </c>
+      <c r="B233" t="s">
+        <v>41</v>
+      </c>
+      <c r="C233">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="D233">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E233" t="s">
+        <v>16</v>
+      </c>
+      <c r="F233">
+        <v>2.5</v>
+      </c>
+      <c r="G233">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>12</v>
+      </c>
+      <c r="B234" t="s">
+        <v>24</v>
+      </c>
+      <c r="C234">
+        <v>0.72142857142857142</v>
+      </c>
+      <c r="D234">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E234" t="s">
+        <v>16</v>
+      </c>
+      <c r="F234">
+        <v>2.5</v>
+      </c>
+      <c r="G234">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>12</v>
+      </c>
+      <c r="B235" t="s">
+        <v>37</v>
+      </c>
+      <c r="C235">
+        <v>0.7686507936507937</v>
+      </c>
+      <c r="D235">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E235" t="s">
+        <v>16</v>
+      </c>
+      <c r="F235">
+        <v>2.5</v>
+      </c>
+      <c r="G235">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" t="s">
+        <v>25</v>
+      </c>
+      <c r="C236">
+        <v>0.72896825396825404</v>
+      </c>
+      <c r="D236">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E236" t="s">
+        <v>16</v>
+      </c>
+      <c r="F236">
+        <v>2.5</v>
+      </c>
+      <c r="G236">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>12</v>
+      </c>
+      <c r="B237" t="s">
+        <v>13</v>
+      </c>
+      <c r="C237">
+        <v>0.61150793650793644</v>
+      </c>
+      <c r="D237">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E237" t="s">
+        <v>16</v>
+      </c>
+      <c r="F237">
+        <v>2.5</v>
+      </c>
+      <c r="G237">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>12</v>
+      </c>
+      <c r="B238" t="s">
+        <v>24</v>
+      </c>
+      <c r="C238">
+        <v>0.81944444444444431</v>
+      </c>
+      <c r="D238">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E238" t="s">
+        <v>16</v>
+      </c>
+      <c r="F238">
+        <v>2.5</v>
+      </c>
+      <c r="G238">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>12</v>
+      </c>
+      <c r="B239" t="s">
+        <v>84</v>
+      </c>
+      <c r="C239">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="D239">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E239" t="s">
+        <v>16</v>
+      </c>
+      <c r="F239">
+        <v>2.5</v>
+      </c>
+      <c r="G239">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>12</v>
+      </c>
+      <c r="B240" t="s">
+        <v>22</v>
+      </c>
+      <c r="C240">
+        <v>0.68928571428571439</v>
+      </c>
+      <c r="D240">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E240" t="s">
+        <v>16</v>
+      </c>
+      <c r="F240">
+        <v>2.5</v>
+      </c>
+      <c r="G240">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>12</v>
+      </c>
+      <c r="B241" t="s">
+        <v>37</v>
+      </c>
+      <c r="C241">
+        <v>0.81785714285714295</v>
+      </c>
+      <c r="D241">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E241" t="s">
+        <v>16</v>
+      </c>
+      <c r="F241">
+        <v>2.5</v>
+      </c>
+      <c r="G241">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242" t="s">
+        <v>13</v>
+      </c>
+      <c r="C242">
+        <v>0.55119047619047623</v>
+      </c>
+      <c r="D242">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E242" t="s">
+        <v>16</v>
+      </c>
+      <c r="F242">
+        <v>2.5</v>
+      </c>
+      <c r="G242">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>12</v>
+      </c>
+      <c r="B243" t="s">
+        <v>43</v>
+      </c>
+      <c r="C243">
+        <v>0.69444444444444431</v>
+      </c>
+      <c r="D243">
+        <v>0.5</v>
+      </c>
+      <c r="E243" t="s">
+        <v>16</v>
+      </c>
+      <c r="F243">
+        <v>2.5</v>
+      </c>
+      <c r="G243">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>12</v>
+      </c>
+      <c r="B244" t="s">
+        <v>40</v>
+      </c>
+      <c r="C244">
+        <v>0.68333333333333324</v>
+      </c>
+      <c r="D244">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E244" t="s">
+        <v>16</v>
+      </c>
+      <c r="F244">
+        <v>2.5</v>
+      </c>
+      <c r="G244">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>12</v>
+      </c>
+      <c r="B245" t="s">
+        <v>40</v>
+      </c>
+      <c r="C245">
+        <v>0.68809523809523798</v>
+      </c>
+      <c r="D245">
+        <v>0.5</v>
+      </c>
+      <c r="E245" t="s">
+        <v>16</v>
+      </c>
+      <c r="F245">
+        <v>2.5</v>
+      </c>
+      <c r="G245">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>12</v>
+      </c>
+      <c r="B246" t="s">
+        <v>38</v>
+      </c>
+      <c r="C246">
+        <v>0.75198412698412698</v>
+      </c>
+      <c r="D246">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E246" t="s">
+        <v>16</v>
+      </c>
+      <c r="F246">
+        <v>2.5</v>
+      </c>
+      <c r="G246">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>12</v>
+      </c>
+      <c r="B247" t="s">
+        <v>32</v>
+      </c>
+      <c r="C247">
+        <v>0.71984126984126984</v>
+      </c>
+      <c r="D247">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E247" t="s">
+        <v>16</v>
+      </c>
+      <c r="F247">
+        <v>2.5</v>
+      </c>
+      <c r="G247">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>12</v>
+      </c>
+      <c r="B248" t="s">
+        <v>22</v>
+      </c>
+      <c r="C248">
+        <v>0.63650793650793647</v>
+      </c>
+      <c r="D248">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E248" t="s">
+        <v>16</v>
+      </c>
+      <c r="F248">
+        <v>2.5</v>
+      </c>
+      <c r="G248">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>12</v>
+      </c>
+      <c r="B249" t="s">
+        <v>22</v>
+      </c>
+      <c r="C249">
+        <v>0.70793650793650797</v>
+      </c>
+      <c r="D249">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E249" t="s">
+        <v>16</v>
+      </c>
+      <c r="F249">
+        <v>2.5</v>
+      </c>
+      <c r="G249">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>12</v>
+      </c>
+      <c r="B250" t="s">
+        <v>29</v>
+      </c>
+      <c r="C250">
+        <v>0.58769841269841272</v>
+      </c>
+      <c r="D250">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E250" t="s">
+        <v>16</v>
+      </c>
+      <c r="F250">
+        <v>2.5</v>
+      </c>
+      <c r="G250">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>12</v>
+      </c>
+      <c r="B251" t="s">
+        <v>37</v>
+      </c>
+      <c r="C251">
+        <v>0.62777777777777777</v>
+      </c>
+      <c r="D251">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E251" t="s">
+        <v>16</v>
+      </c>
+      <c r="F251">
+        <v>2.5</v>
+      </c>
+      <c r="G251">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>12</v>
+      </c>
+      <c r="B252" t="s">
+        <v>29</v>
+      </c>
+      <c r="C252">
+        <v>0.82539682539682546</v>
+      </c>
+      <c r="D252">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E252" t="s">
+        <v>16</v>
+      </c>
+      <c r="F252">
+        <v>2.5</v>
+      </c>
+      <c r="G252">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>12</v>
+      </c>
+      <c r="B253" t="s">
+        <v>27</v>
+      </c>
+      <c r="C253">
+        <v>0.6694444444444444</v>
+      </c>
+      <c r="D253">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E253" t="s">
+        <v>16</v>
+      </c>
+      <c r="F253">
+        <v>2.5</v>
+      </c>
+      <c r="G253">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>12</v>
+      </c>
+      <c r="B254" t="s">
+        <v>41</v>
+      </c>
+      <c r="C254">
+        <v>0.72817460317460314</v>
+      </c>
+      <c r="D254">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E254" t="s">
+        <v>16</v>
+      </c>
+      <c r="F254">
+        <v>2.5</v>
+      </c>
+      <c r="G254">
+        <v>20</v>
+      </c>
+      <c r="H254" t="s">
+        <v>85</v>
+      </c>
+      <c r="I254" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B255" t="s">
+        <v>46</v>
+      </c>
+      <c r="C255">
+        <v>0.55595238095238098</v>
+      </c>
+      <c r="D255">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E255" t="s">
+        <v>16</v>
+      </c>
+      <c r="F255">
+        <v>2.5</v>
+      </c>
+      <c r="G255">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B256" t="s">
+        <v>51</v>
+      </c>
+      <c r="C256">
+        <v>0.67539682539682533</v>
+      </c>
+      <c r="D256">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E256" t="s">
+        <v>16</v>
+      </c>
+      <c r="F256">
+        <v>2.5</v>
+      </c>
+      <c r="G256">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>9</v>
+      </c>
+      <c r="B257" t="s">
+        <v>64</v>
+      </c>
+      <c r="C257">
+        <v>0.63452380952380949</v>
+      </c>
+      <c r="D257">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E257" t="s">
+        <v>16</v>
+      </c>
+      <c r="F257">
+        <v>2.5</v>
+      </c>
+      <c r="G257">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B258" t="s">
+        <v>87</v>
+      </c>
+      <c r="C258">
+        <v>0.7587301587301587</v>
+      </c>
+      <c r="D258">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E258" t="s">
+        <v>16</v>
+      </c>
+      <c r="F258">
+        <v>2.5</v>
+      </c>
+      <c r="G258">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" t="s">
+        <v>46</v>
+      </c>
+      <c r="C259">
+        <v>0.72896825396825404</v>
+      </c>
+      <c r="D259">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E259" t="s">
+        <v>16</v>
+      </c>
+      <c r="F259">
+        <v>2.5</v>
+      </c>
+      <c r="G259">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B260" t="s">
+        <v>88</v>
+      </c>
+      <c r="C260">
+        <v>0.68730158730158741</v>
+      </c>
+      <c r="D260">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E260" t="s">
+        <v>16</v>
+      </c>
+      <c r="F260">
+        <v>2.5</v>
+      </c>
+      <c r="G260">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>9</v>
+      </c>
+      <c r="B261" t="s">
+        <v>88</v>
+      </c>
+      <c r="C261">
+        <v>0.63690476190476197</v>
+      </c>
+      <c r="D261">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E261" t="s">
+        <v>16</v>
+      </c>
+      <c r="F261">
+        <v>2.5</v>
+      </c>
+      <c r="G261">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>9</v>
+      </c>
+      <c r="B262" t="s">
+        <v>89</v>
+      </c>
+      <c r="C262">
+        <v>0.67261904761904778</v>
+      </c>
+      <c r="D262">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E262" t="s">
+        <v>16</v>
+      </c>
+      <c r="F262">
+        <v>2.5</v>
+      </c>
+      <c r="G262">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>9</v>
+      </c>
+      <c r="B263" t="s">
+        <v>50</v>
+      </c>
+      <c r="C263">
+        <v>0.74880952380952392</v>
+      </c>
+      <c r="D263">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E263" t="s">
+        <v>16</v>
+      </c>
+      <c r="F263">
+        <v>2.5</v>
+      </c>
+      <c r="G263">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>9</v>
+      </c>
+      <c r="B264" t="s">
+        <v>67</v>
+      </c>
+      <c r="C264">
+        <v>0.7587301587301587</v>
+      </c>
+      <c r="D264">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E264" t="s">
+        <v>16</v>
+      </c>
+      <c r="F264">
+        <v>2.5</v>
+      </c>
+      <c r="G264">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>9</v>
+      </c>
+      <c r="B265" t="s">
+        <v>53</v>
+      </c>
+      <c r="C265">
+        <v>0.68928571428571439</v>
+      </c>
+      <c r="D265">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E265" t="s">
+        <v>16</v>
+      </c>
+      <c r="F265">
+        <v>2.5</v>
+      </c>
+      <c r="G265">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>9</v>
+      </c>
+      <c r="B266" t="s">
+        <v>55</v>
+      </c>
+      <c r="C266">
+        <v>0.62857142857142856</v>
+      </c>
+      <c r="D266">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E266" t="s">
+        <v>16</v>
+      </c>
+      <c r="F266">
+        <v>2.5</v>
+      </c>
+      <c r="G266">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>9</v>
+      </c>
+      <c r="B267" t="s">
+        <v>90</v>
+      </c>
+      <c r="C267">
+        <v>0.69166666666666676</v>
+      </c>
+      <c r="D267">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E267" t="s">
+        <v>16</v>
+      </c>
+      <c r="F267">
+        <v>2.5</v>
+      </c>
+      <c r="G267">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>9</v>
+      </c>
+      <c r="B268" t="s">
+        <v>63</v>
+      </c>
+      <c r="C268">
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="D268">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E268" t="s">
+        <v>16</v>
+      </c>
+      <c r="F268">
+        <v>2.5</v>
+      </c>
+      <c r="G268">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>9</v>
+      </c>
+      <c r="B269" t="s">
+        <v>58</v>
+      </c>
+      <c r="C269">
+        <v>0.70119047619047625</v>
+      </c>
+      <c r="D269">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E269" t="s">
+        <v>16</v>
+      </c>
+      <c r="F269">
+        <v>2.5</v>
+      </c>
+      <c r="G269">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>9</v>
+      </c>
+      <c r="B270" t="s">
+        <v>56</v>
+      </c>
+      <c r="C270">
+        <v>0.73888888888888893</v>
+      </c>
+      <c r="D270">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E270" t="s">
+        <v>16</v>
+      </c>
+      <c r="F270">
+        <v>2.5</v>
+      </c>
+      <c r="G270">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>9</v>
+      </c>
+      <c r="B271" t="s">
+        <v>91</v>
+      </c>
+      <c r="C271">
+        <v>0.61865079365079367</v>
+      </c>
+      <c r="D271">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E271" t="s">
+        <v>16</v>
+      </c>
+      <c r="F271">
+        <v>2.5</v>
+      </c>
+      <c r="G271">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>9</v>
+      </c>
+      <c r="B272" t="s">
+        <v>92</v>
+      </c>
+      <c r="C272">
+        <v>0.77857142857142858</v>
+      </c>
+      <c r="D272">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E272" t="s">
+        <v>16</v>
+      </c>
+      <c r="F272">
+        <v>2.5</v>
+      </c>
+      <c r="G272">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>9</v>
+      </c>
+      <c r="B273" t="s">
+        <v>72</v>
+      </c>
+      <c r="C273">
+        <v>0.63968253968253974</v>
+      </c>
+      <c r="D273">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E273" t="s">
+        <v>16</v>
+      </c>
+      <c r="F273">
+        <v>2.5</v>
+      </c>
+      <c r="G273">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>9</v>
+      </c>
+      <c r="B274" t="s">
+        <v>93</v>
+      </c>
+      <c r="C274">
+        <v>0.77619047619047621</v>
+      </c>
+      <c r="D274">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E274" t="s">
+        <v>16</v>
+      </c>
+      <c r="F274">
+        <v>2.5</v>
+      </c>
+      <c r="G274">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>9</v>
+      </c>
+      <c r="B275" t="s">
+        <v>58</v>
+      </c>
+      <c r="C275">
+        <v>0.67420634920634914</v>
+      </c>
+      <c r="D275">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E275" t="s">
+        <v>16</v>
+      </c>
+      <c r="F275">
+        <v>2.5</v>
+      </c>
+      <c r="G275">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>9</v>
+      </c>
+      <c r="B276" t="s">
+        <v>94</v>
+      </c>
+      <c r="C276">
+        <v>0.63214285714285712</v>
+      </c>
+      <c r="D276">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E276" t="s">
+        <v>16</v>
+      </c>
+      <c r="F276">
+        <v>2.5</v>
+      </c>
+      <c r="G276">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>9</v>
+      </c>
+      <c r="B277" t="s">
+        <v>58</v>
+      </c>
+      <c r="C277">
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="D277">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E277" t="s">
+        <v>16</v>
+      </c>
+      <c r="F277">
+        <v>2.5</v>
+      </c>
+      <c r="G277">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>9</v>
+      </c>
+      <c r="B278" t="s">
+        <v>53</v>
+      </c>
+      <c r="C278">
+        <v>0.69484126984126993</v>
+      </c>
+      <c r="D278">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E278" t="s">
+        <v>16</v>
+      </c>
+      <c r="F278">
+        <v>2.5</v>
+      </c>
+      <c r="G278">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>9</v>
+      </c>
+      <c r="B279" t="s">
+        <v>93</v>
+      </c>
+      <c r="C279">
+        <v>0.71904761904761916</v>
+      </c>
+      <c r="D279">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E279" t="s">
+        <v>16</v>
+      </c>
+      <c r="F279">
+        <v>2.5</v>
+      </c>
+      <c r="G279">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>9</v>
+      </c>
+      <c r="B280" t="s">
+        <v>64</v>
+      </c>
+      <c r="C280">
+        <v>0.6432539682539683</v>
+      </c>
+      <c r="D280">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E280" t="s">
+        <v>16</v>
+      </c>
+      <c r="F280">
+        <v>2.5</v>
+      </c>
+      <c r="G280">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>9</v>
+      </c>
+      <c r="B281" t="s">
+        <v>95</v>
+      </c>
+      <c r="C281">
+        <v>0.59087301587301588</v>
+      </c>
+      <c r="D281">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E281" t="s">
+        <v>16</v>
+      </c>
+      <c r="F281">
+        <v>2.5</v>
+      </c>
+      <c r="G281">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>9</v>
+      </c>
+      <c r="B282" t="s">
+        <v>46</v>
+      </c>
+      <c r="C282">
+        <v>0.58015873015873021</v>
+      </c>
+      <c r="D282">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E282" t="s">
+        <v>16</v>
+      </c>
+      <c r="F282">
+        <v>2.5</v>
+      </c>
+      <c r="G282">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>9</v>
+      </c>
+      <c r="B283" t="s">
+        <v>92</v>
+      </c>
+      <c r="C283">
+        <v>0.58015873015873021</v>
+      </c>
+      <c r="D283">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E283" t="s">
+        <v>16</v>
+      </c>
+      <c r="F283">
+        <v>2.5</v>
+      </c>
+      <c r="G283">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>9</v>
+      </c>
+      <c r="B284" t="s">
+        <v>92</v>
+      </c>
+      <c r="C284">
+        <v>0.73174603174603181</v>
+      </c>
+      <c r="D284">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E284" t="s">
+        <v>16</v>
+      </c>
+      <c r="F284">
+        <v>2.5</v>
+      </c>
+      <c r="G284">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>9</v>
+      </c>
+      <c r="B285" t="s">
+        <v>56</v>
+      </c>
+      <c r="C285">
+        <v>0.70992063492063495</v>
+      </c>
+      <c r="D285">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E285" t="s">
+        <v>16</v>
+      </c>
+      <c r="F285">
+        <v>2.5</v>
+      </c>
+      <c r="G285">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>9</v>
+      </c>
+      <c r="B286" t="s">
+        <v>96</v>
+      </c>
+      <c r="C286">
+        <v>0.71904761904761905</v>
+      </c>
+      <c r="D286">
+        <v>0.46969696969696972</v>
+      </c>
+      <c r="E286" t="s">
+        <v>16</v>
+      </c>
+      <c r="F286">
+        <v>2.5</v>
+      </c>
+      <c r="G286">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>9</v>
+      </c>
+      <c r="B287" t="s">
+        <v>69</v>
+      </c>
+      <c r="C287">
+        <v>0.71309523809523812</v>
+      </c>
+      <c r="D287">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E287" t="s">
+        <v>16</v>
+      </c>
+      <c r="F287">
+        <v>2.5</v>
+      </c>
+      <c r="G287">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>9</v>
+      </c>
+      <c r="B288" t="s">
+        <v>97</v>
+      </c>
+      <c r="C288">
+        <v>0.74880952380952381</v>
+      </c>
+      <c r="D288">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E288" t="s">
+        <v>16</v>
+      </c>
+      <c r="F288">
+        <v>2.5</v>
+      </c>
+      <c r="G288">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>9</v>
+      </c>
+      <c r="B289" t="s">
+        <v>49</v>
+      </c>
+      <c r="C289">
+        <v>0.81230158730158719</v>
+      </c>
+      <c r="D289">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E289" t="s">
+        <v>16</v>
+      </c>
+      <c r="F289">
+        <v>2.5</v>
+      </c>
+      <c r="G289">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>9</v>
+      </c>
+      <c r="B290" t="s">
+        <v>98</v>
+      </c>
+      <c r="C290">
+        <v>0.66190476190476188</v>
+      </c>
+      <c r="D290">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E290" t="s">
+        <v>16</v>
+      </c>
+      <c r="F290">
+        <v>2.5</v>
+      </c>
+      <c r="G290">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>9</v>
+      </c>
+      <c r="B291" t="s">
+        <v>72</v>
+      </c>
+      <c r="C291">
+        <v>0.75674603174603172</v>
+      </c>
+      <c r="D291">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E291" t="s">
+        <v>16</v>
+      </c>
+      <c r="F291">
+        <v>2.5</v>
+      </c>
+      <c r="G291">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>9</v>
+      </c>
+      <c r="B292" t="s">
+        <v>51</v>
+      </c>
+      <c r="C292">
+        <v>0.64563492063492067</v>
+      </c>
+      <c r="D292">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E292" t="s">
+        <v>16</v>
+      </c>
+      <c r="F292">
+        <v>2.5</v>
+      </c>
+      <c r="G292">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>9</v>
+      </c>
+      <c r="B293" t="s">
+        <v>97</v>
+      </c>
+      <c r="C293">
+        <v>0.75714285714285712</v>
+      </c>
+      <c r="D293">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E293" t="s">
+        <v>16</v>
+      </c>
+      <c r="F293">
+        <v>2.5</v>
+      </c>
+      <c r="G293">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>9</v>
+      </c>
+      <c r="B294" t="s">
+        <v>64</v>
+      </c>
+      <c r="C294">
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="D294">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E294" t="s">
+        <v>16</v>
+      </c>
+      <c r="F294">
+        <v>2.5</v>
+      </c>
+      <c r="G294">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>9</v>
+      </c>
+      <c r="B295" t="s">
+        <v>99</v>
+      </c>
+      <c r="C295">
+        <v>0.62936507936507935</v>
+      </c>
+      <c r="D295">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E295" t="s">
+        <v>16</v>
+      </c>
+      <c r="F295">
+        <v>2.5</v>
+      </c>
+      <c r="G295">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>9</v>
+      </c>
+      <c r="B296" t="s">
+        <v>100</v>
+      </c>
+      <c r="C296">
+        <v>0.80595238095238086</v>
+      </c>
+      <c r="D296">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E296" t="s">
+        <v>16</v>
+      </c>
+      <c r="F296">
+        <v>2.5</v>
+      </c>
+      <c r="G296">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>9</v>
+      </c>
+      <c r="B297" t="s">
+        <v>93</v>
+      </c>
+      <c r="C297">
+        <v>0.70952380952380956</v>
+      </c>
+      <c r="D297">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E297" t="s">
+        <v>16</v>
+      </c>
+      <c r="F297">
+        <v>2.5</v>
+      </c>
+      <c r="G297">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>9</v>
+      </c>
+      <c r="B298" t="s">
+        <v>62</v>
+      </c>
+      <c r="C298">
+        <v>0.78214285714285714</v>
+      </c>
+      <c r="D298">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E298" t="s">
+        <v>16</v>
+      </c>
+      <c r="F298">
+        <v>2.5</v>
+      </c>
+      <c r="G298">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>9</v>
+      </c>
+      <c r="B299" t="s">
+        <v>101</v>
+      </c>
+      <c r="C299">
+        <v>0.70912698412698416</v>
+      </c>
+      <c r="D299">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E299" t="s">
+        <v>16</v>
+      </c>
+      <c r="F299">
+        <v>2.5</v>
+      </c>
+      <c r="G299">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300" t="s">
+        <v>102</v>
+      </c>
+      <c r="C300">
+        <v>0.65357142857142858</v>
+      </c>
+      <c r="D300">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E300" t="s">
+        <v>16</v>
+      </c>
+      <c r="F300">
+        <v>2.5</v>
+      </c>
+      <c r="G300">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>9</v>
+      </c>
+      <c r="B301" t="s">
+        <v>92</v>
+      </c>
+      <c r="C301">
+        <v>0.67142857142857137</v>
+      </c>
+      <c r="D301">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E301" t="s">
+        <v>16</v>
+      </c>
+      <c r="F301">
+        <v>2.5</v>
+      </c>
+      <c r="G301">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>9</v>
+      </c>
+      <c r="B302" t="s">
+        <v>103</v>
+      </c>
+      <c r="C302">
+        <v>0.8047619047619049</v>
+      </c>
+      <c r="D302">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E302" t="s">
+        <v>16</v>
+      </c>
+      <c r="F302">
+        <v>2.5</v>
+      </c>
+      <c r="G302">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>9</v>
+      </c>
+      <c r="B303" t="s">
+        <v>95</v>
+      </c>
+      <c r="C303">
+        <v>0.63452380952380949</v>
+      </c>
+      <c r="D303">
+        <v>0.43939393939393928</v>
+      </c>
+      <c r="E303" t="s">
+        <v>16</v>
+      </c>
+      <c r="F303">
+        <v>2.5</v>
+      </c>
+      <c r="G303">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>9</v>
+      </c>
+      <c r="B304" t="s">
+        <v>50</v>
+      </c>
+      <c r="C304">
+        <v>0.77738095238095239</v>
+      </c>
+      <c r="D304">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E304" t="s">
+        <v>16</v>
+      </c>
+      <c r="F304">
+        <v>2.5</v>
+      </c>
+      <c r="G304">
+        <v>20</v>
+      </c>
+      <c r="H304" t="s">
+        <v>104</v>
+      </c>
+      <c r="I304" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_49B9D71E964C440E62355476585DCE3A87458BAF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8333085E-90FA-4C27-9545-504AB8F6BB04}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_08C1AEB71759AA0F62355476585DCE3A874466E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3335836-0023-4678-AD19-6D4DE6904158}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="126">
   <si>
     <t>Model</t>
   </si>
@@ -338,6 +338,66 @@
   </si>
   <si>
     <t>0.1636</t>
+  </si>
+  <si>
+    <t>{'svm__C': 0.1, 'svm__gamma': 'scale', 'svm__kernel': 'rbf'}</t>
+  </si>
+  <si>
+    <t>0.7330</t>
+  </si>
+  <si>
+    <t>0.1492</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 1, 'rf__min_samples_split': 10, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 4, 'rf__min_samples_split': 2, 'rf__n_estimators': 300}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'sqrt', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 5, 'rf__n_estimators': 100}</t>
+  </si>
+  <si>
+    <t>{'rf__max_depth': None, 'rf__max_features': 'log2', 'rf__min_samples_leaf': 2, 'rf__min_samples_split': 2, 'rf__n_estimators': 500}</t>
+  </si>
+  <si>
+    <t>0.6736</t>
+  </si>
+  <si>
+    <t>0.1523</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.6, 'xgb__learning_rate': 0.05, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 100, 'xgb__subsample': 1.0}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 0.8, 'xgb__learning_rate': 0.1, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 500, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.6}</t>
+  </si>
+  <si>
+    <t>{'xgb__colsample_bytree': 1.0, 'xgb__learning_rate': 0.01, 'xgb__max_depth': 3, 'xgb__min_child_weight': 1, 'xgb__n_estimators': 300, 'xgb__subsample': 0.8}</t>
+  </si>
+  <si>
+    <t>0.6873</t>
+  </si>
+  <si>
+    <t>0.1743</t>
   </si>
 </sst>
 </file>
@@ -700,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I304"/>
+  <dimension ref="A1:I454"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -7743,6 +7803,3474 @@
         <v>105</v>
       </c>
     </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>14</v>
+      </c>
+      <c r="B305" t="s">
+        <v>15</v>
+      </c>
+      <c r="C305">
+        <v>0.69841269841269848</v>
+      </c>
+      <c r="D305">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E305" t="s">
+        <v>16</v>
+      </c>
+      <c r="F305">
+        <v>2.5</v>
+      </c>
+      <c r="G305">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>14</v>
+      </c>
+      <c r="B306" t="s">
+        <v>15</v>
+      </c>
+      <c r="C306">
+        <v>0.75158730158730158</v>
+      </c>
+      <c r="D306">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="E306" t="s">
+        <v>16</v>
+      </c>
+      <c r="F306">
+        <v>2.5</v>
+      </c>
+      <c r="G306">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>14</v>
+      </c>
+      <c r="B307" t="s">
+        <v>15</v>
+      </c>
+      <c r="C307">
+        <v>0.75992063492063489</v>
+      </c>
+      <c r="D307">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E307" t="s">
+        <v>16</v>
+      </c>
+      <c r="F307">
+        <v>2.5</v>
+      </c>
+      <c r="G307">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>14</v>
+      </c>
+      <c r="B308" t="s">
+        <v>15</v>
+      </c>
+      <c r="C308">
+        <v>0.54523809523809519</v>
+      </c>
+      <c r="D308">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E308" t="s">
+        <v>16</v>
+      </c>
+      <c r="F308">
+        <v>2.5</v>
+      </c>
+      <c r="G308">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>14</v>
+      </c>
+      <c r="B309" t="s">
+        <v>15</v>
+      </c>
+      <c r="C309">
+        <v>0.79920634920634936</v>
+      </c>
+      <c r="D309">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E309" t="s">
+        <v>16</v>
+      </c>
+      <c r="F309">
+        <v>2.5</v>
+      </c>
+      <c r="G309">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>14</v>
+      </c>
+      <c r="B310" t="s">
+        <v>15</v>
+      </c>
+      <c r="C310">
+        <v>0.57341269841269837</v>
+      </c>
+      <c r="D310">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E310" t="s">
+        <v>16</v>
+      </c>
+      <c r="F310">
+        <v>2.5</v>
+      </c>
+      <c r="G310">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>14</v>
+      </c>
+      <c r="B311" t="s">
+        <v>15</v>
+      </c>
+      <c r="C311">
+        <v>0.57817460317460323</v>
+      </c>
+      <c r="D311">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E311" t="s">
+        <v>16</v>
+      </c>
+      <c r="F311">
+        <v>2.5</v>
+      </c>
+      <c r="G311">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>14</v>
+      </c>
+      <c r="B312" t="s">
+        <v>15</v>
+      </c>
+      <c r="C312">
+        <v>0.77380952380952372</v>
+      </c>
+      <c r="D312">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E312" t="s">
+        <v>16</v>
+      </c>
+      <c r="F312">
+        <v>2.5</v>
+      </c>
+      <c r="G312">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>14</v>
+      </c>
+      <c r="B313" t="s">
+        <v>15</v>
+      </c>
+      <c r="C313">
+        <v>0.69404761904761914</v>
+      </c>
+      <c r="D313">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E313" t="s">
+        <v>16</v>
+      </c>
+      <c r="F313">
+        <v>2.5</v>
+      </c>
+      <c r="G313">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>14</v>
+      </c>
+      <c r="B314" t="s">
+        <v>15</v>
+      </c>
+      <c r="C314">
+        <v>0.67738095238095231</v>
+      </c>
+      <c r="D314">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E314" t="s">
+        <v>16</v>
+      </c>
+      <c r="F314">
+        <v>2.5</v>
+      </c>
+      <c r="G314">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>14</v>
+      </c>
+      <c r="B315" t="s">
+        <v>106</v>
+      </c>
+      <c r="C315">
+        <v>0.5</v>
+      </c>
+      <c r="D315">
+        <v>0.5</v>
+      </c>
+      <c r="E315" t="s">
+        <v>16</v>
+      </c>
+      <c r="F315">
+        <v>2.5</v>
+      </c>
+      <c r="G315">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>14</v>
+      </c>
+      <c r="B316" t="s">
+        <v>15</v>
+      </c>
+      <c r="C316">
+        <v>0.79682539682539699</v>
+      </c>
+      <c r="D316">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E316" t="s">
+        <v>16</v>
+      </c>
+      <c r="F316">
+        <v>2.5</v>
+      </c>
+      <c r="G316">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>14</v>
+      </c>
+      <c r="B317" t="s">
+        <v>15</v>
+      </c>
+      <c r="C317">
+        <v>0.56111111111111112</v>
+      </c>
+      <c r="D317">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="E317" t="s">
+        <v>16</v>
+      </c>
+      <c r="F317">
+        <v>2.5</v>
+      </c>
+      <c r="G317">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>14</v>
+      </c>
+      <c r="B318" t="s">
+        <v>15</v>
+      </c>
+      <c r="C318">
+        <v>0.59761904761904761</v>
+      </c>
+      <c r="D318">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E318" t="s">
+        <v>16</v>
+      </c>
+      <c r="F318">
+        <v>2.5</v>
+      </c>
+      <c r="G318">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>14</v>
+      </c>
+      <c r="B319" t="s">
+        <v>15</v>
+      </c>
+      <c r="C319">
+        <v>0.72658730158730156</v>
+      </c>
+      <c r="D319">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E319" t="s">
+        <v>16</v>
+      </c>
+      <c r="F319">
+        <v>2.5</v>
+      </c>
+      <c r="G319">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>14</v>
+      </c>
+      <c r="B320" t="s">
+        <v>15</v>
+      </c>
+      <c r="C320">
+        <v>0.60238095238095235</v>
+      </c>
+      <c r="D320">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E320" t="s">
+        <v>16</v>
+      </c>
+      <c r="F320">
+        <v>2.5</v>
+      </c>
+      <c r="G320">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>14</v>
+      </c>
+      <c r="B321" t="s">
+        <v>15</v>
+      </c>
+      <c r="C321">
+        <v>0.73571428571428577</v>
+      </c>
+      <c r="D321">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E321" t="s">
+        <v>16</v>
+      </c>
+      <c r="F321">
+        <v>2.5</v>
+      </c>
+      <c r="G321">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>14</v>
+      </c>
+      <c r="B322" t="s">
+        <v>15</v>
+      </c>
+      <c r="C322">
+        <v>0.598015873015873</v>
+      </c>
+      <c r="D322">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E322" t="s">
+        <v>16</v>
+      </c>
+      <c r="F322">
+        <v>2.5</v>
+      </c>
+      <c r="G322">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>14</v>
+      </c>
+      <c r="B323" t="s">
+        <v>15</v>
+      </c>
+      <c r="C323">
+        <v>0.66190476190476188</v>
+      </c>
+      <c r="D323">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E323" t="s">
+        <v>16</v>
+      </c>
+      <c r="F323">
+        <v>2.5</v>
+      </c>
+      <c r="G323">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>14</v>
+      </c>
+      <c r="B324" t="s">
+        <v>15</v>
+      </c>
+      <c r="C324">
+        <v>0.74722222222222223</v>
+      </c>
+      <c r="D324">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E324" t="s">
+        <v>16</v>
+      </c>
+      <c r="F324">
+        <v>2.5</v>
+      </c>
+      <c r="G324">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>14</v>
+      </c>
+      <c r="B325" t="s">
+        <v>15</v>
+      </c>
+      <c r="C325">
+        <v>0.67301587301587296</v>
+      </c>
+      <c r="D325">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E325" t="s">
+        <v>16</v>
+      </c>
+      <c r="F325">
+        <v>2.5</v>
+      </c>
+      <c r="G325">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>14</v>
+      </c>
+      <c r="B326" t="s">
+        <v>15</v>
+      </c>
+      <c r="C326">
+        <v>0.5984126984126984</v>
+      </c>
+      <c r="D326">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E326" t="s">
+        <v>16</v>
+      </c>
+      <c r="F326">
+        <v>2.5</v>
+      </c>
+      <c r="G326">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>14</v>
+      </c>
+      <c r="B327" t="s">
+        <v>15</v>
+      </c>
+      <c r="C327">
+        <v>0.759920634920635</v>
+      </c>
+      <c r="D327">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E327" t="s">
+        <v>16</v>
+      </c>
+      <c r="F327">
+        <v>2.5</v>
+      </c>
+      <c r="G327">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>14</v>
+      </c>
+      <c r="B328" t="s">
+        <v>15</v>
+      </c>
+      <c r="C328">
+        <v>0.73730158730158735</v>
+      </c>
+      <c r="D328">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E328" t="s">
+        <v>16</v>
+      </c>
+      <c r="F328">
+        <v>2.5</v>
+      </c>
+      <c r="G328">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>14</v>
+      </c>
+      <c r="B329" t="s">
+        <v>15</v>
+      </c>
+      <c r="C329">
+        <v>0.73492063492063497</v>
+      </c>
+      <c r="D329">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E329" t="s">
+        <v>16</v>
+      </c>
+      <c r="F329">
+        <v>2.5</v>
+      </c>
+      <c r="G329">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>14</v>
+      </c>
+      <c r="B330" t="s">
+        <v>15</v>
+      </c>
+      <c r="C330">
+        <v>0.79484126984126979</v>
+      </c>
+      <c r="D330">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E330" t="s">
+        <v>16</v>
+      </c>
+      <c r="F330">
+        <v>2.5</v>
+      </c>
+      <c r="G330">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>14</v>
+      </c>
+      <c r="B331" t="s">
+        <v>15</v>
+      </c>
+      <c r="C331">
+        <v>0.57579365079365075</v>
+      </c>
+      <c r="D331">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E331" t="s">
+        <v>16</v>
+      </c>
+      <c r="F331">
+        <v>2.5</v>
+      </c>
+      <c r="G331">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>14</v>
+      </c>
+      <c r="B332" t="s">
+        <v>15</v>
+      </c>
+      <c r="C332">
+        <v>0.68492063492063482</v>
+      </c>
+      <c r="D332">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E332" t="s">
+        <v>16</v>
+      </c>
+      <c r="F332">
+        <v>2.5</v>
+      </c>
+      <c r="G332">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>14</v>
+      </c>
+      <c r="B333" t="s">
+        <v>15</v>
+      </c>
+      <c r="C333">
+        <v>0.7325396825396826</v>
+      </c>
+      <c r="D333">
+        <v>1</v>
+      </c>
+      <c r="E333" t="s">
+        <v>16</v>
+      </c>
+      <c r="F333">
+        <v>2.5</v>
+      </c>
+      <c r="G333">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>14</v>
+      </c>
+      <c r="B334" t="s">
+        <v>15</v>
+      </c>
+      <c r="C334">
+        <v>0.85873015873015868</v>
+      </c>
+      <c r="D334">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E334" t="s">
+        <v>16</v>
+      </c>
+      <c r="F334">
+        <v>2.5</v>
+      </c>
+      <c r="G334">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>14</v>
+      </c>
+      <c r="B335" t="s">
+        <v>15</v>
+      </c>
+      <c r="C335">
+        <v>0.76428571428571423</v>
+      </c>
+      <c r="D335">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E335" t="s">
+        <v>16</v>
+      </c>
+      <c r="F335">
+        <v>2.5</v>
+      </c>
+      <c r="G335">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>14</v>
+      </c>
+      <c r="B336" t="s">
+        <v>15</v>
+      </c>
+      <c r="C336">
+        <v>0.64960317460317463</v>
+      </c>
+      <c r="D336">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E336" t="s">
+        <v>16</v>
+      </c>
+      <c r="F336">
+        <v>2.5</v>
+      </c>
+      <c r="G336">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>14</v>
+      </c>
+      <c r="B337" t="s">
+        <v>15</v>
+      </c>
+      <c r="C337">
+        <v>0.62817460317460316</v>
+      </c>
+      <c r="D337">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E337" t="s">
+        <v>16</v>
+      </c>
+      <c r="F337">
+        <v>2.5</v>
+      </c>
+      <c r="G337">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>14</v>
+      </c>
+      <c r="B338" t="s">
+        <v>15</v>
+      </c>
+      <c r="C338">
+        <v>0.77896825396825398</v>
+      </c>
+      <c r="D338">
+        <v>0.68181818181818188</v>
+      </c>
+      <c r="E338" t="s">
+        <v>16</v>
+      </c>
+      <c r="F338">
+        <v>2.5</v>
+      </c>
+      <c r="G338">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>14</v>
+      </c>
+      <c r="B339" t="s">
+        <v>15</v>
+      </c>
+      <c r="C339">
+        <v>0.6869047619047618</v>
+      </c>
+      <c r="D339">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E339" t="s">
+        <v>16</v>
+      </c>
+      <c r="F339">
+        <v>2.5</v>
+      </c>
+      <c r="G339">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>14</v>
+      </c>
+      <c r="B340" t="s">
+        <v>15</v>
+      </c>
+      <c r="C340">
+        <v>0.68571428571428561</v>
+      </c>
+      <c r="D340">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E340" t="s">
+        <v>16</v>
+      </c>
+      <c r="F340">
+        <v>2.5</v>
+      </c>
+      <c r="G340">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>14</v>
+      </c>
+      <c r="B341" t="s">
+        <v>15</v>
+      </c>
+      <c r="C341">
+        <v>0.73849206349206353</v>
+      </c>
+      <c r="D341">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E341" t="s">
+        <v>16</v>
+      </c>
+      <c r="F341">
+        <v>2.5</v>
+      </c>
+      <c r="G341">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>14</v>
+      </c>
+      <c r="B342" t="s">
+        <v>15</v>
+      </c>
+      <c r="C342">
+        <v>0.64960317460317463</v>
+      </c>
+      <c r="D342">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E342" t="s">
+        <v>16</v>
+      </c>
+      <c r="F342">
+        <v>2.5</v>
+      </c>
+      <c r="G342">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>14</v>
+      </c>
+      <c r="B343" t="s">
+        <v>15</v>
+      </c>
+      <c r="C343">
+        <v>0.78214285714285714</v>
+      </c>
+      <c r="D343">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E343" t="s">
+        <v>16</v>
+      </c>
+      <c r="F343">
+        <v>2.5</v>
+      </c>
+      <c r="G343">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>14</v>
+      </c>
+      <c r="B344" t="s">
+        <v>15</v>
+      </c>
+      <c r="C344">
+        <v>0.54603174603174598</v>
+      </c>
+      <c r="D344">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E344" t="s">
+        <v>16</v>
+      </c>
+      <c r="F344">
+        <v>2.5</v>
+      </c>
+      <c r="G344">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>14</v>
+      </c>
+      <c r="B345" t="s">
+        <v>15</v>
+      </c>
+      <c r="C345">
+        <v>0.64047619047619042</v>
+      </c>
+      <c r="D345">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E345" t="s">
+        <v>16</v>
+      </c>
+      <c r="F345">
+        <v>2.5</v>
+      </c>
+      <c r="G345">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>14</v>
+      </c>
+      <c r="B346" t="s">
+        <v>15</v>
+      </c>
+      <c r="C346">
+        <v>0.85793650793650789</v>
+      </c>
+      <c r="D346">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E346" t="s">
+        <v>16</v>
+      </c>
+      <c r="F346">
+        <v>2.5</v>
+      </c>
+      <c r="G346">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>14</v>
+      </c>
+      <c r="B347" t="s">
+        <v>15</v>
+      </c>
+      <c r="C347">
+        <v>0.63809523809523805</v>
+      </c>
+      <c r="D347">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E347" t="s">
+        <v>16</v>
+      </c>
+      <c r="F347">
+        <v>2.5</v>
+      </c>
+      <c r="G347">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>14</v>
+      </c>
+      <c r="B348" t="s">
+        <v>15</v>
+      </c>
+      <c r="C348">
+        <v>0.75238095238095237</v>
+      </c>
+      <c r="D348">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E348" t="s">
+        <v>16</v>
+      </c>
+      <c r="F348">
+        <v>2.5</v>
+      </c>
+      <c r="G348">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>14</v>
+      </c>
+      <c r="B349" t="s">
+        <v>15</v>
+      </c>
+      <c r="C349">
+        <v>0.67738095238095253</v>
+      </c>
+      <c r="D349">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E349" t="s">
+        <v>16</v>
+      </c>
+      <c r="F349">
+        <v>2.5</v>
+      </c>
+      <c r="G349">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>14</v>
+      </c>
+      <c r="B350" t="s">
+        <v>15</v>
+      </c>
+      <c r="C350">
+        <v>0.53650793650793649</v>
+      </c>
+      <c r="D350">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E350" t="s">
+        <v>16</v>
+      </c>
+      <c r="F350">
+        <v>2.5</v>
+      </c>
+      <c r="G350">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>14</v>
+      </c>
+      <c r="B351" t="s">
+        <v>15</v>
+      </c>
+      <c r="C351">
+        <v>0.75952380952380949</v>
+      </c>
+      <c r="D351">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E351" t="s">
+        <v>16</v>
+      </c>
+      <c r="F351">
+        <v>2.5</v>
+      </c>
+      <c r="G351">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>14</v>
+      </c>
+      <c r="B352" t="s">
+        <v>15</v>
+      </c>
+      <c r="C352">
+        <v>0.73174603174603181</v>
+      </c>
+      <c r="D352">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E352" t="s">
+        <v>16</v>
+      </c>
+      <c r="F352">
+        <v>2.5</v>
+      </c>
+      <c r="G352">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>14</v>
+      </c>
+      <c r="B353" t="s">
+        <v>15</v>
+      </c>
+      <c r="C353">
+        <v>0.61865079365079367</v>
+      </c>
+      <c r="D353">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E353" t="s">
+        <v>16</v>
+      </c>
+      <c r="F353">
+        <v>2.5</v>
+      </c>
+      <c r="G353">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>14</v>
+      </c>
+      <c r="B354" t="s">
+        <v>15</v>
+      </c>
+      <c r="C354">
+        <v>0.6880952380952382</v>
+      </c>
+      <c r="D354">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E354" t="s">
+        <v>16</v>
+      </c>
+      <c r="F354">
+        <v>2.5</v>
+      </c>
+      <c r="G354">
+        <v>40</v>
+      </c>
+      <c r="H354" t="s">
+        <v>107</v>
+      </c>
+      <c r="I354" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>12</v>
+      </c>
+      <c r="B355" t="s">
+        <v>43</v>
+      </c>
+      <c r="C355">
+        <v>0.62698412698412698</v>
+      </c>
+      <c r="D355">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E355" t="s">
+        <v>16</v>
+      </c>
+      <c r="F355">
+        <v>2.5</v>
+      </c>
+      <c r="G355">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>12</v>
+      </c>
+      <c r="B356" t="s">
+        <v>109</v>
+      </c>
+      <c r="C356">
+        <v>0.71507936507936509</v>
+      </c>
+      <c r="D356">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E356" t="s">
+        <v>16</v>
+      </c>
+      <c r="F356">
+        <v>2.5</v>
+      </c>
+      <c r="G356">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>12</v>
+      </c>
+      <c r="B357" t="s">
+        <v>82</v>
+      </c>
+      <c r="C357">
+        <v>0.75396825396825395</v>
+      </c>
+      <c r="D357">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E357" t="s">
+        <v>16</v>
+      </c>
+      <c r="F357">
+        <v>2.5</v>
+      </c>
+      <c r="G357">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>12</v>
+      </c>
+      <c r="B358" t="s">
+        <v>22</v>
+      </c>
+      <c r="C358">
+        <v>0.67063492063492058</v>
+      </c>
+      <c r="D358">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E358" t="s">
+        <v>16</v>
+      </c>
+      <c r="F358">
+        <v>2.5</v>
+      </c>
+      <c r="G358">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>12</v>
+      </c>
+      <c r="B359" t="s">
+        <v>22</v>
+      </c>
+      <c r="C359">
+        <v>0.82341269841269848</v>
+      </c>
+      <c r="D359">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E359" t="s">
+        <v>16</v>
+      </c>
+      <c r="F359">
+        <v>2.5</v>
+      </c>
+      <c r="G359">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>12</v>
+      </c>
+      <c r="B360" t="s">
+        <v>29</v>
+      </c>
+      <c r="C360">
+        <v>0.67539682539682533</v>
+      </c>
+      <c r="D360">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E360" t="s">
+        <v>16</v>
+      </c>
+      <c r="F360">
+        <v>2.5</v>
+      </c>
+      <c r="G360">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>12</v>
+      </c>
+      <c r="B361" t="s">
+        <v>26</v>
+      </c>
+      <c r="C361">
+        <v>0.66349206349206347</v>
+      </c>
+      <c r="D361">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E361" t="s">
+        <v>16</v>
+      </c>
+      <c r="F361">
+        <v>2.5</v>
+      </c>
+      <c r="G361">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>12</v>
+      </c>
+      <c r="B362" t="s">
+        <v>29</v>
+      </c>
+      <c r="C362">
+        <v>0.59285714285714286</v>
+      </c>
+      <c r="D362">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E362" t="s">
+        <v>16</v>
+      </c>
+      <c r="F362">
+        <v>2.5</v>
+      </c>
+      <c r="G362">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>12</v>
+      </c>
+      <c r="B363" t="s">
+        <v>110</v>
+      </c>
+      <c r="C363">
+        <v>0.71230158730158732</v>
+      </c>
+      <c r="D363">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E363" t="s">
+        <v>16</v>
+      </c>
+      <c r="F363">
+        <v>2.5</v>
+      </c>
+      <c r="G363">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>12</v>
+      </c>
+      <c r="B364" t="s">
+        <v>37</v>
+      </c>
+      <c r="C364">
+        <v>0.72896825396825404</v>
+      </c>
+      <c r="D364">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E364" t="s">
+        <v>16</v>
+      </c>
+      <c r="F364">
+        <v>2.5</v>
+      </c>
+      <c r="G364">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>12</v>
+      </c>
+      <c r="B365" t="s">
+        <v>29</v>
+      </c>
+      <c r="C365">
+        <v>0.60317460317460314</v>
+      </c>
+      <c r="D365">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E365" t="s">
+        <v>16</v>
+      </c>
+      <c r="F365">
+        <v>2.5</v>
+      </c>
+      <c r="G365">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>12</v>
+      </c>
+      <c r="B366" t="s">
+        <v>35</v>
+      </c>
+      <c r="C366">
+        <v>0.71587301587301588</v>
+      </c>
+      <c r="D366">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E366" t="s">
+        <v>16</v>
+      </c>
+      <c r="F366">
+        <v>2.5</v>
+      </c>
+      <c r="G366">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>12</v>
+      </c>
+      <c r="B367" t="s">
+        <v>83</v>
+      </c>
+      <c r="C367">
+        <v>0.65476190476190477</v>
+      </c>
+      <c r="D367">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E367" t="s">
+        <v>16</v>
+      </c>
+      <c r="F367">
+        <v>2.5</v>
+      </c>
+      <c r="G367">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>12</v>
+      </c>
+      <c r="B368" t="s">
+        <v>25</v>
+      </c>
+      <c r="C368">
+        <v>0.69761904761904747</v>
+      </c>
+      <c r="D368">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E368" t="s">
+        <v>16</v>
+      </c>
+      <c r="F368">
+        <v>2.5</v>
+      </c>
+      <c r="G368">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>12</v>
+      </c>
+      <c r="B369" t="s">
+        <v>80</v>
+      </c>
+      <c r="C369">
+        <v>0.80753968253968245</v>
+      </c>
+      <c r="D369">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E369" t="s">
+        <v>16</v>
+      </c>
+      <c r="F369">
+        <v>2.5</v>
+      </c>
+      <c r="G369">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>12</v>
+      </c>
+      <c r="B370" t="s">
+        <v>24</v>
+      </c>
+      <c r="C370">
+        <v>0.58611111111111114</v>
+      </c>
+      <c r="D370">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E370" t="s">
+        <v>16</v>
+      </c>
+      <c r="F370">
+        <v>2.5</v>
+      </c>
+      <c r="G370">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>12</v>
+      </c>
+      <c r="B371" t="s">
+        <v>21</v>
+      </c>
+      <c r="C371">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D371">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E371" t="s">
+        <v>16</v>
+      </c>
+      <c r="F371">
+        <v>2.5</v>
+      </c>
+      <c r="G371">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>12</v>
+      </c>
+      <c r="B372" t="s">
+        <v>109</v>
+      </c>
+      <c r="C372">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="D372">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E372" t="s">
+        <v>16</v>
+      </c>
+      <c r="F372">
+        <v>2.5</v>
+      </c>
+      <c r="G372">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>12</v>
+      </c>
+      <c r="B373" t="s">
+        <v>38</v>
+      </c>
+      <c r="C373">
+        <v>0.74682539682539684</v>
+      </c>
+      <c r="D373">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E373" t="s">
+        <v>16</v>
+      </c>
+      <c r="F373">
+        <v>2.5</v>
+      </c>
+      <c r="G373">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>12</v>
+      </c>
+      <c r="B374" t="s">
+        <v>38</v>
+      </c>
+      <c r="C374">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="D374">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E374" t="s">
+        <v>16</v>
+      </c>
+      <c r="F374">
+        <v>2.5</v>
+      </c>
+      <c r="G374">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>12</v>
+      </c>
+      <c r="B375" t="s">
+        <v>40</v>
+      </c>
+      <c r="C375">
+        <v>0.69285714285714295</v>
+      </c>
+      <c r="D375">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E375" t="s">
+        <v>16</v>
+      </c>
+      <c r="F375">
+        <v>2.5</v>
+      </c>
+      <c r="G375">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>12</v>
+      </c>
+      <c r="B376" t="s">
+        <v>111</v>
+      </c>
+      <c r="C376">
+        <v>0.57420634920634928</v>
+      </c>
+      <c r="D376">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E376" t="s">
+        <v>16</v>
+      </c>
+      <c r="F376">
+        <v>2.5</v>
+      </c>
+      <c r="G376">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>12</v>
+      </c>
+      <c r="B377" t="s">
+        <v>82</v>
+      </c>
+      <c r="C377">
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="D377">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E377" t="s">
+        <v>16</v>
+      </c>
+      <c r="F377">
+        <v>2.5</v>
+      </c>
+      <c r="G377">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>12</v>
+      </c>
+      <c r="B378" t="s">
+        <v>112</v>
+      </c>
+      <c r="C378">
+        <v>0.72896825396825393</v>
+      </c>
+      <c r="D378">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="E378" t="s">
+        <v>16</v>
+      </c>
+      <c r="F378">
+        <v>2.5</v>
+      </c>
+      <c r="G378">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>12</v>
+      </c>
+      <c r="B379" t="s">
+        <v>37</v>
+      </c>
+      <c r="C379">
+        <v>0.67817460317460332</v>
+      </c>
+      <c r="D379">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E379" t="s">
+        <v>16</v>
+      </c>
+      <c r="F379">
+        <v>2.5</v>
+      </c>
+      <c r="G379">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>12</v>
+      </c>
+      <c r="B380" t="s">
+        <v>22</v>
+      </c>
+      <c r="C380">
+        <v>0.76507936507936503</v>
+      </c>
+      <c r="D380">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E380" t="s">
+        <v>16</v>
+      </c>
+      <c r="F380">
+        <v>2.5</v>
+      </c>
+      <c r="G380">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>12</v>
+      </c>
+      <c r="B381" t="s">
+        <v>113</v>
+      </c>
+      <c r="C381">
+        <v>0.81587301587301597</v>
+      </c>
+      <c r="D381">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E381" t="s">
+        <v>16</v>
+      </c>
+      <c r="F381">
+        <v>2.5</v>
+      </c>
+      <c r="G381">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>12</v>
+      </c>
+      <c r="B382" t="s">
+        <v>24</v>
+      </c>
+      <c r="C382">
+        <v>0.73333333333333339</v>
+      </c>
+      <c r="D382">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E382" t="s">
+        <v>16</v>
+      </c>
+      <c r="F382">
+        <v>2.5</v>
+      </c>
+      <c r="G382">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>12</v>
+      </c>
+      <c r="B383" t="s">
+        <v>33</v>
+      </c>
+      <c r="C383">
+        <v>0.74722222222222223</v>
+      </c>
+      <c r="D383">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E383" t="s">
+        <v>16</v>
+      </c>
+      <c r="F383">
+        <v>2.5</v>
+      </c>
+      <c r="G383">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>12</v>
+      </c>
+      <c r="B384" t="s">
+        <v>13</v>
+      </c>
+      <c r="C384">
+        <v>0.71587301587301588</v>
+      </c>
+      <c r="D384">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E384" t="s">
+        <v>16</v>
+      </c>
+      <c r="F384">
+        <v>2.5</v>
+      </c>
+      <c r="G384">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>12</v>
+      </c>
+      <c r="B385" t="s">
+        <v>37</v>
+      </c>
+      <c r="C385">
+        <v>0.70119047619047625</v>
+      </c>
+      <c r="D385">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E385" t="s">
+        <v>16</v>
+      </c>
+      <c r="F385">
+        <v>2.5</v>
+      </c>
+      <c r="G385">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>12</v>
+      </c>
+      <c r="B386" t="s">
+        <v>24</v>
+      </c>
+      <c r="C386">
+        <v>0.71785714285714286</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>16</v>
+      </c>
+      <c r="F386">
+        <v>2.5</v>
+      </c>
+      <c r="G386">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>12</v>
+      </c>
+      <c r="B387" t="s">
+        <v>29</v>
+      </c>
+      <c r="C387">
+        <v>0.62063492063492065</v>
+      </c>
+      <c r="D387">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E387" t="s">
+        <v>16</v>
+      </c>
+      <c r="F387">
+        <v>2.5</v>
+      </c>
+      <c r="G387">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>12</v>
+      </c>
+      <c r="B388" t="s">
+        <v>40</v>
+      </c>
+      <c r="C388">
+        <v>0.79563492063492058</v>
+      </c>
+      <c r="D388">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E388" t="s">
+        <v>16</v>
+      </c>
+      <c r="F388">
+        <v>2.5</v>
+      </c>
+      <c r="G388">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>12</v>
+      </c>
+      <c r="B389" t="s">
+        <v>34</v>
+      </c>
+      <c r="C389">
+        <v>0.81111111111111123</v>
+      </c>
+      <c r="D389">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E389" t="s">
+        <v>16</v>
+      </c>
+      <c r="F389">
+        <v>2.5</v>
+      </c>
+      <c r="G389">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>12</v>
+      </c>
+      <c r="B390" t="s">
+        <v>38</v>
+      </c>
+      <c r="C390">
+        <v>0.70198412698412704</v>
+      </c>
+      <c r="D390">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E390" t="s">
+        <v>16</v>
+      </c>
+      <c r="F390">
+        <v>2.5</v>
+      </c>
+      <c r="G390">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>12</v>
+      </c>
+      <c r="B391" t="s">
+        <v>28</v>
+      </c>
+      <c r="C391">
+        <v>0.71865079365079365</v>
+      </c>
+      <c r="D391">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E391" t="s">
+        <v>16</v>
+      </c>
+      <c r="F391">
+        <v>2.5</v>
+      </c>
+      <c r="G391">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>12</v>
+      </c>
+      <c r="B392" t="s">
+        <v>114</v>
+      </c>
+      <c r="C392">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D392">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E392" t="s">
+        <v>16</v>
+      </c>
+      <c r="F392">
+        <v>2.5</v>
+      </c>
+      <c r="G392">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>12</v>
+      </c>
+      <c r="B393" t="s">
+        <v>38</v>
+      </c>
+      <c r="C393">
+        <v>0.76944444444444449</v>
+      </c>
+      <c r="D393">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E393" t="s">
+        <v>16</v>
+      </c>
+      <c r="F393">
+        <v>2.5</v>
+      </c>
+      <c r="G393">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>12</v>
+      </c>
+      <c r="B394" t="s">
+        <v>109</v>
+      </c>
+      <c r="C394">
+        <v>0.64563492063492067</v>
+      </c>
+      <c r="D394">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E394" t="s">
+        <v>16</v>
+      </c>
+      <c r="F394">
+        <v>2.5</v>
+      </c>
+      <c r="G394">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>12</v>
+      </c>
+      <c r="B395" t="s">
+        <v>26</v>
+      </c>
+      <c r="C395">
+        <v>0.75198412698412698</v>
+      </c>
+      <c r="D395">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E395" t="s">
+        <v>16</v>
+      </c>
+      <c r="F395">
+        <v>2.5</v>
+      </c>
+      <c r="G395">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>12</v>
+      </c>
+      <c r="B396" t="s">
+        <v>34</v>
+      </c>
+      <c r="C396">
+        <v>0.79365079365079361</v>
+      </c>
+      <c r="D396">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E396" t="s">
+        <v>16</v>
+      </c>
+      <c r="F396">
+        <v>2.5</v>
+      </c>
+      <c r="G396">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>12</v>
+      </c>
+      <c r="B397" t="s">
+        <v>29</v>
+      </c>
+      <c r="C397">
+        <v>0.73174603174603181</v>
+      </c>
+      <c r="D397">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E397" t="s">
+        <v>16</v>
+      </c>
+      <c r="F397">
+        <v>2.5</v>
+      </c>
+      <c r="G397">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>12</v>
+      </c>
+      <c r="B398" t="s">
+        <v>37</v>
+      </c>
+      <c r="C398">
+        <v>0.79761904761904756</v>
+      </c>
+      <c r="D398">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E398" t="s">
+        <v>16</v>
+      </c>
+      <c r="F398">
+        <v>2.5</v>
+      </c>
+      <c r="G398">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>12</v>
+      </c>
+      <c r="B399" t="s">
+        <v>37</v>
+      </c>
+      <c r="C399">
+        <v>0.63492063492063489</v>
+      </c>
+      <c r="D399">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E399" t="s">
+        <v>16</v>
+      </c>
+      <c r="F399">
+        <v>2.5</v>
+      </c>
+      <c r="G399">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>12</v>
+      </c>
+      <c r="B400" t="s">
+        <v>43</v>
+      </c>
+      <c r="C400">
+        <v>0.50753968253968262</v>
+      </c>
+      <c r="D400">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E400" t="s">
+        <v>16</v>
+      </c>
+      <c r="F400">
+        <v>2.5</v>
+      </c>
+      <c r="G400">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>12</v>
+      </c>
+      <c r="B401" t="s">
+        <v>38</v>
+      </c>
+      <c r="C401">
+        <v>0.68333333333333324</v>
+      </c>
+      <c r="D401">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E401" t="s">
+        <v>16</v>
+      </c>
+      <c r="F401">
+        <v>2.5</v>
+      </c>
+      <c r="G401">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>12</v>
+      </c>
+      <c r="B402" t="s">
+        <v>37</v>
+      </c>
+      <c r="C402">
+        <v>0.78134920634920635</v>
+      </c>
+      <c r="D402">
+        <v>0.5</v>
+      </c>
+      <c r="E402" t="s">
+        <v>16</v>
+      </c>
+      <c r="F402">
+        <v>2.5</v>
+      </c>
+      <c r="G402">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>12</v>
+      </c>
+      <c r="B403" t="s">
+        <v>25</v>
+      </c>
+      <c r="C403">
+        <v>0.60198412698412707</v>
+      </c>
+      <c r="D403">
+        <v>0.74242424242424243</v>
+      </c>
+      <c r="E403" t="s">
+        <v>16</v>
+      </c>
+      <c r="F403">
+        <v>2.5</v>
+      </c>
+      <c r="G403">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>12</v>
+      </c>
+      <c r="B404" t="s">
+        <v>41</v>
+      </c>
+      <c r="C404">
+        <v>0.74206349206349209</v>
+      </c>
+      <c r="D404">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E404" t="s">
+        <v>16</v>
+      </c>
+      <c r="F404">
+        <v>2.5</v>
+      </c>
+      <c r="G404">
+        <v>40</v>
+      </c>
+      <c r="H404" t="s">
+        <v>115</v>
+      </c>
+      <c r="I404" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>9</v>
+      </c>
+      <c r="B405" t="s">
+        <v>117</v>
+      </c>
+      <c r="C405">
+        <v>0.73888888888888893</v>
+      </c>
+      <c r="D405">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E405" t="s">
+        <v>16</v>
+      </c>
+      <c r="F405">
+        <v>2.5</v>
+      </c>
+      <c r="G405">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>9</v>
+      </c>
+      <c r="B406" t="s">
+        <v>10</v>
+      </c>
+      <c r="C406">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="D406">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E406" t="s">
+        <v>16</v>
+      </c>
+      <c r="F406">
+        <v>2.5</v>
+      </c>
+      <c r="G406">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>9</v>
+      </c>
+      <c r="B407" t="s">
+        <v>47</v>
+      </c>
+      <c r="C407">
+        <v>0.73492063492063497</v>
+      </c>
+      <c r="D407">
+        <v>0.39393939393939392</v>
+      </c>
+      <c r="E407" t="s">
+        <v>16</v>
+      </c>
+      <c r="F407">
+        <v>2.5</v>
+      </c>
+      <c r="G407">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>9</v>
+      </c>
+      <c r="B408" t="s">
+        <v>55</v>
+      </c>
+      <c r="C408">
+        <v>0.81349206349206338</v>
+      </c>
+      <c r="D408">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E408" t="s">
+        <v>16</v>
+      </c>
+      <c r="F408">
+        <v>2.5</v>
+      </c>
+      <c r="G408">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>9</v>
+      </c>
+      <c r="B409" t="s">
+        <v>91</v>
+      </c>
+      <c r="C409">
+        <v>0.82539682539682546</v>
+      </c>
+      <c r="D409">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E409" t="s">
+        <v>16</v>
+      </c>
+      <c r="F409">
+        <v>2.5</v>
+      </c>
+      <c r="G409">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>9</v>
+      </c>
+      <c r="B410" t="s">
+        <v>60</v>
+      </c>
+      <c r="C410">
+        <v>0.67619047619047612</v>
+      </c>
+      <c r="D410">
+        <v>0.45454545454545447</v>
+      </c>
+      <c r="E410" t="s">
+        <v>16</v>
+      </c>
+      <c r="F410">
+        <v>2.5</v>
+      </c>
+      <c r="G410">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>9</v>
+      </c>
+      <c r="B411" t="s">
+        <v>118</v>
+      </c>
+      <c r="C411">
+        <v>0.56626984126984126</v>
+      </c>
+      <c r="D411">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E411" t="s">
+        <v>16</v>
+      </c>
+      <c r="F411">
+        <v>2.5</v>
+      </c>
+      <c r="G411">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>9</v>
+      </c>
+      <c r="B412" t="s">
+        <v>48</v>
+      </c>
+      <c r="C412">
+        <v>0.78015873015873016</v>
+      </c>
+      <c r="D412">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E412" t="s">
+        <v>16</v>
+      </c>
+      <c r="F412">
+        <v>2.5</v>
+      </c>
+      <c r="G412">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>9</v>
+      </c>
+      <c r="B413" t="s">
+        <v>94</v>
+      </c>
+      <c r="C413">
+        <v>0.77936507936507937</v>
+      </c>
+      <c r="D413">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E413" t="s">
+        <v>16</v>
+      </c>
+      <c r="F413">
+        <v>2.5</v>
+      </c>
+      <c r="G413">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>9</v>
+      </c>
+      <c r="B414" t="s">
+        <v>51</v>
+      </c>
+      <c r="C414">
+        <v>0.77539682539682542</v>
+      </c>
+      <c r="D414">
+        <v>0.51515151515151514</v>
+      </c>
+      <c r="E414" t="s">
+        <v>16</v>
+      </c>
+      <c r="F414">
+        <v>2.5</v>
+      </c>
+      <c r="G414">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>9</v>
+      </c>
+      <c r="B415" t="s">
+        <v>50</v>
+      </c>
+      <c r="C415">
+        <v>0.66428571428571426</v>
+      </c>
+      <c r="D415">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E415" t="s">
+        <v>16</v>
+      </c>
+      <c r="F415">
+        <v>2.5</v>
+      </c>
+      <c r="G415">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>9</v>
+      </c>
+      <c r="B416" t="s">
+        <v>67</v>
+      </c>
+      <c r="C416">
+        <v>0.68571428571428561</v>
+      </c>
+      <c r="D416">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E416" t="s">
+        <v>16</v>
+      </c>
+      <c r="F416">
+        <v>2.5</v>
+      </c>
+      <c r="G416">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>9</v>
+      </c>
+      <c r="B417" t="s">
+        <v>88</v>
+      </c>
+      <c r="C417">
+        <v>0.73492063492063497</v>
+      </c>
+      <c r="D417">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="E417" t="s">
+        <v>16</v>
+      </c>
+      <c r="F417">
+        <v>2.5</v>
+      </c>
+      <c r="G417">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>9</v>
+      </c>
+      <c r="B418" t="s">
+        <v>63</v>
+      </c>
+      <c r="C418">
+        <v>0.61944444444444446</v>
+      </c>
+      <c r="D418">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E418" t="s">
+        <v>16</v>
+      </c>
+      <c r="F418">
+        <v>2.5</v>
+      </c>
+      <c r="G418">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>9</v>
+      </c>
+      <c r="B419" t="s">
+        <v>48</v>
+      </c>
+      <c r="C419">
+        <v>0.7146825396825397</v>
+      </c>
+      <c r="D419">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E419" t="s">
+        <v>16</v>
+      </c>
+      <c r="F419">
+        <v>2.5</v>
+      </c>
+      <c r="G419">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>9</v>
+      </c>
+      <c r="B420" t="s">
+        <v>103</v>
+      </c>
+      <c r="C420">
+        <v>0.73888888888888893</v>
+      </c>
+      <c r="D420">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E420" t="s">
+        <v>16</v>
+      </c>
+      <c r="F420">
+        <v>2.5</v>
+      </c>
+      <c r="G420">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>9</v>
+      </c>
+      <c r="B421" t="s">
+        <v>48</v>
+      </c>
+      <c r="C421">
+        <v>0.76230158730158737</v>
+      </c>
+      <c r="D421">
+        <v>0.56060606060606055</v>
+      </c>
+      <c r="E421" t="s">
+        <v>16</v>
+      </c>
+      <c r="F421">
+        <v>2.5</v>
+      </c>
+      <c r="G421">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>9</v>
+      </c>
+      <c r="B422" t="s">
+        <v>72</v>
+      </c>
+      <c r="C422">
+        <v>0.84523809523809523</v>
+      </c>
+      <c r="D422">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="E422" t="s">
+        <v>16</v>
+      </c>
+      <c r="F422">
+        <v>2.5</v>
+      </c>
+      <c r="G422">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>9</v>
+      </c>
+      <c r="B423" t="s">
+        <v>52</v>
+      </c>
+      <c r="C423">
+        <v>0.64126984126984132</v>
+      </c>
+      <c r="D423">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E423" t="s">
+        <v>16</v>
+      </c>
+      <c r="F423">
+        <v>2.5</v>
+      </c>
+      <c r="G423">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>9</v>
+      </c>
+      <c r="B424" t="s">
+        <v>72</v>
+      </c>
+      <c r="C424">
+        <v>0.70873015873015877</v>
+      </c>
+      <c r="D424">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E424" t="s">
+        <v>16</v>
+      </c>
+      <c r="F424">
+        <v>2.5</v>
+      </c>
+      <c r="G424">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>9</v>
+      </c>
+      <c r="B425" t="s">
+        <v>72</v>
+      </c>
+      <c r="C425">
+        <v>0.71666666666666679</v>
+      </c>
+      <c r="D425">
+        <v>1</v>
+      </c>
+      <c r="E425" t="s">
+        <v>16</v>
+      </c>
+      <c r="F425">
+        <v>2.5</v>
+      </c>
+      <c r="G425">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>9</v>
+      </c>
+      <c r="B426" t="s">
+        <v>119</v>
+      </c>
+      <c r="C426">
+        <v>0.61388888888888882</v>
+      </c>
+      <c r="D426">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E426" t="s">
+        <v>16</v>
+      </c>
+      <c r="F426">
+        <v>2.5</v>
+      </c>
+      <c r="G426">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>9</v>
+      </c>
+      <c r="B427" t="s">
+        <v>52</v>
+      </c>
+      <c r="C427">
+        <v>0.70317460317460323</v>
+      </c>
+      <c r="D427">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="E427" t="s">
+        <v>16</v>
+      </c>
+      <c r="F427">
+        <v>2.5</v>
+      </c>
+      <c r="G427">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>9</v>
+      </c>
+      <c r="B428" t="s">
+        <v>50</v>
+      </c>
+      <c r="C428">
+        <v>0.66587301587301584</v>
+      </c>
+      <c r="D428">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E428" t="s">
+        <v>16</v>
+      </c>
+      <c r="F428">
+        <v>2.5</v>
+      </c>
+      <c r="G428">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>9</v>
+      </c>
+      <c r="B429" t="s">
+        <v>70</v>
+      </c>
+      <c r="C429">
+        <v>0.64841269841269844</v>
+      </c>
+      <c r="D429">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E429" t="s">
+        <v>16</v>
+      </c>
+      <c r="F429">
+        <v>2.5</v>
+      </c>
+      <c r="G429">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>9</v>
+      </c>
+      <c r="B430" t="s">
+        <v>58</v>
+      </c>
+      <c r="C430">
+        <v>0.58690476190476193</v>
+      </c>
+      <c r="D430">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E430" t="s">
+        <v>16</v>
+      </c>
+      <c r="F430">
+        <v>2.5</v>
+      </c>
+      <c r="G430">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>9</v>
+      </c>
+      <c r="B431" t="s">
+        <v>59</v>
+      </c>
+      <c r="C431">
+        <v>0.67896825396825411</v>
+      </c>
+      <c r="D431">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E431" t="s">
+        <v>16</v>
+      </c>
+      <c r="F431">
+        <v>2.5</v>
+      </c>
+      <c r="G431">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>9</v>
+      </c>
+      <c r="B432" t="s">
+        <v>64</v>
+      </c>
+      <c r="C432">
+        <v>0.66547619047619044</v>
+      </c>
+      <c r="D432">
+        <v>0.51515151515151514</v>
+      </c>
+      <c r="E432" t="s">
+        <v>16</v>
+      </c>
+      <c r="F432">
+        <v>2.5</v>
+      </c>
+      <c r="G432">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>9</v>
+      </c>
+      <c r="B433" t="s">
+        <v>87</v>
+      </c>
+      <c r="C433">
+        <v>0.65634920634920635</v>
+      </c>
+      <c r="D433">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E433" t="s">
+        <v>16</v>
+      </c>
+      <c r="F433">
+        <v>2.5</v>
+      </c>
+      <c r="G433">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>9</v>
+      </c>
+      <c r="B434" t="s">
+        <v>53</v>
+      </c>
+      <c r="C434">
+        <v>0.79246031746031742</v>
+      </c>
+      <c r="D434">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E434" t="s">
+        <v>16</v>
+      </c>
+      <c r="F434">
+        <v>2.5</v>
+      </c>
+      <c r="G434">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>9</v>
+      </c>
+      <c r="B435" t="s">
+        <v>120</v>
+      </c>
+      <c r="C435">
+        <v>0.77460317460317463</v>
+      </c>
+      <c r="D435">
+        <v>0.60606060606060597</v>
+      </c>
+      <c r="E435" t="s">
+        <v>16</v>
+      </c>
+      <c r="F435">
+        <v>2.5</v>
+      </c>
+      <c r="G435">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>9</v>
+      </c>
+      <c r="B436" t="s">
+        <v>50</v>
+      </c>
+      <c r="C436">
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="D436">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E436" t="s">
+        <v>16</v>
+      </c>
+      <c r="F436">
+        <v>2.5</v>
+      </c>
+      <c r="G436">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>9</v>
+      </c>
+      <c r="B437" t="s">
+        <v>121</v>
+      </c>
+      <c r="C437">
+        <v>0.64484126984126977</v>
+      </c>
+      <c r="D437">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E437" t="s">
+        <v>16</v>
+      </c>
+      <c r="F437">
+        <v>2.5</v>
+      </c>
+      <c r="G437">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>9</v>
+      </c>
+      <c r="B438" t="s">
+        <v>58</v>
+      </c>
+      <c r="C438">
+        <v>0.77460317460317463</v>
+      </c>
+      <c r="D438">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E438" t="s">
+        <v>16</v>
+      </c>
+      <c r="F438">
+        <v>2.5</v>
+      </c>
+      <c r="G438">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>9</v>
+      </c>
+      <c r="B439" t="s">
+        <v>10</v>
+      </c>
+      <c r="C439">
+        <v>0.78373015873015872</v>
+      </c>
+      <c r="D439">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E439" t="s">
+        <v>16</v>
+      </c>
+      <c r="F439">
+        <v>2.5</v>
+      </c>
+      <c r="G439">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>9</v>
+      </c>
+      <c r="B440" t="s">
+        <v>71</v>
+      </c>
+      <c r="C440">
+        <v>0.65952380952380951</v>
+      </c>
+      <c r="D440">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E440" t="s">
+        <v>16</v>
+      </c>
+      <c r="F440">
+        <v>2.5</v>
+      </c>
+      <c r="G440">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>9</v>
+      </c>
+      <c r="B441" t="s">
+        <v>122</v>
+      </c>
+      <c r="C441">
+        <v>0.71309523809523812</v>
+      </c>
+      <c r="D441">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="E441" t="s">
+        <v>16</v>
+      </c>
+      <c r="F441">
+        <v>2.5</v>
+      </c>
+      <c r="G441">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>9</v>
+      </c>
+      <c r="B442" t="s">
+        <v>72</v>
+      </c>
+      <c r="C442">
+        <v>0.66349206349206347</v>
+      </c>
+      <c r="D442">
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="E442" t="s">
+        <v>16</v>
+      </c>
+      <c r="F442">
+        <v>2.5</v>
+      </c>
+      <c r="G442">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>9</v>
+      </c>
+      <c r="B443" t="s">
+        <v>10</v>
+      </c>
+      <c r="C443">
+        <v>0.76428571428571435</v>
+      </c>
+      <c r="D443">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E443" t="s">
+        <v>16</v>
+      </c>
+      <c r="F443">
+        <v>2.5</v>
+      </c>
+      <c r="G443">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>9</v>
+      </c>
+      <c r="B444" t="s">
+        <v>58</v>
+      </c>
+      <c r="C444">
+        <v>0.63650793650793647</v>
+      </c>
+      <c r="D444">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E444" t="s">
+        <v>16</v>
+      </c>
+      <c r="F444">
+        <v>2.5</v>
+      </c>
+      <c r="G444">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>9</v>
+      </c>
+      <c r="B445" t="s">
+        <v>118</v>
+      </c>
+      <c r="C445">
+        <v>0.69761904761904769</v>
+      </c>
+      <c r="D445">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="E445" t="s">
+        <v>16</v>
+      </c>
+      <c r="F445">
+        <v>2.5</v>
+      </c>
+      <c r="G445">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>9</v>
+      </c>
+      <c r="B446" t="s">
+        <v>58</v>
+      </c>
+      <c r="C446">
+        <v>0.78452380952380951</v>
+      </c>
+      <c r="D446">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="E446" t="s">
+        <v>16</v>
+      </c>
+      <c r="F446">
+        <v>2.5</v>
+      </c>
+      <c r="G446">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>9</v>
+      </c>
+      <c r="B447" t="s">
+        <v>123</v>
+      </c>
+      <c r="C447">
+        <v>0.73015873015873023</v>
+      </c>
+      <c r="D447">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E447" t="s">
+        <v>16</v>
+      </c>
+      <c r="F447">
+        <v>2.5</v>
+      </c>
+      <c r="G447">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>9</v>
+      </c>
+      <c r="B448" t="s">
+        <v>67</v>
+      </c>
+      <c r="C448">
+        <v>0.67023809523809519</v>
+      </c>
+      <c r="D448">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="E448" t="s">
+        <v>16</v>
+      </c>
+      <c r="F448">
+        <v>2.5</v>
+      </c>
+      <c r="G448">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>9</v>
+      </c>
+      <c r="B449" t="s">
+        <v>59</v>
+      </c>
+      <c r="C449">
+        <v>0.79047619047619044</v>
+      </c>
+      <c r="D449">
+        <v>0.81818181818181812</v>
+      </c>
+      <c r="E449" t="s">
+        <v>16</v>
+      </c>
+      <c r="F449">
+        <v>2.5</v>
+      </c>
+      <c r="G449">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>9</v>
+      </c>
+      <c r="B450" t="s">
+        <v>48</v>
+      </c>
+      <c r="C450">
+        <v>0.67738095238095253</v>
+      </c>
+      <c r="D450">
+        <v>0.65151515151515149</v>
+      </c>
+      <c r="E450" t="s">
+        <v>16</v>
+      </c>
+      <c r="F450">
+        <v>2.5</v>
+      </c>
+      <c r="G450">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>9</v>
+      </c>
+      <c r="B451" t="s">
+        <v>48</v>
+      </c>
+      <c r="C451">
+        <v>0.82619047619047625</v>
+      </c>
+      <c r="D451">
+        <v>0.48484848484848492</v>
+      </c>
+      <c r="E451" t="s">
+        <v>16</v>
+      </c>
+      <c r="F451">
+        <v>2.5</v>
+      </c>
+      <c r="G451">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>9</v>
+      </c>
+      <c r="B452" t="s">
+        <v>92</v>
+      </c>
+      <c r="C452">
+        <v>0.81190476190476202</v>
+      </c>
+      <c r="D452">
+        <v>0.62121212121212122</v>
+      </c>
+      <c r="E452" t="s">
+        <v>16</v>
+      </c>
+      <c r="F452">
+        <v>2.5</v>
+      </c>
+      <c r="G452">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>9</v>
+      </c>
+      <c r="B453" t="s">
+        <v>10</v>
+      </c>
+      <c r="C453">
+        <v>0.6880952380952382</v>
+      </c>
+      <c r="D453">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E453" t="s">
+        <v>16</v>
+      </c>
+      <c r="F453">
+        <v>2.5</v>
+      </c>
+      <c r="G453">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>9</v>
+      </c>
+      <c r="B454" t="s">
+        <v>67</v>
+      </c>
+      <c r="C454">
+        <v>0.76468253968253974</v>
+      </c>
+      <c r="D454">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E454" t="s">
+        <v>16</v>
+      </c>
+      <c r="F454">
+        <v>2.5</v>
+      </c>
+      <c r="G454">
+        <v>40</v>
+      </c>
+      <c r="H454" t="s">
+        <v>124</v>
+      </c>
+      <c r="I454" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/martina_baroffio_epfl_ch/Documents/EPFL/MA1/ML/ML4Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_08C1AEB71759AA0F62355476585DCE3A874466E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3335836-0023-4678-AD19-6D4DE6904158}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_08C1AEB71759AA0F62355476585DCE3A874466E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2165D0CB-84EE-401C-AC17-FB0B848A5B16}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -762,6 +762,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I454"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="80.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
